--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxepunkter" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sammanfattning" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_Förslag" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxepunkter'!$A$1:$J$242</definedName>
@@ -21,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +34,13 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +50,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,12 +75,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -154,6 +179,45 @@
     <tableColumn id="8" name="EDP koppling status"/>
     <tableColumn id="9" name="Kommentar"/>
     <tableColumn id="10" name="Källa"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TaxaForslagTable" displayName="TaxaForslagTable" ref="A6:K7" headerRowCount="1">
+  <autoFilter ref="A6:K7"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="Paragraf"/>
+    <tableColumn id="3" name="Taxapunkt"/>
+    <tableColumn id="4" name="Variant"/>
+    <tableColumn id="5" name="Enhet"/>
+    <tableColumn id="6" name="Föreslagen taxekod"/>
+    <tableColumn id="7" name="Föreslagen benämning"/>
+    <tableColumn id="8" name="Källa"/>
+    <tableColumn id="9" name="Säkerhet"/>
+    <tableColumn id="10" name="Status"/>
+    <tableColumn id="11" name="Kommentar"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
+  <autoFilter ref="A6:J7"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="Paragraf"/>
+    <tableColumn id="3" name="Taxapunkt"/>
+    <tableColumn id="4" name="Fält"/>
+    <tableColumn id="5" name="Värde"/>
+    <tableColumn id="6" name="Ursprung"/>
+    <tableColumn id="7" name="Regel"/>
+    <tableColumn id="8" name="Källa"/>
+    <tableColumn id="9" name="Status"/>
+    <tableColumn id="10" name="Kommentar"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8818,7 +8882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8866,6 +8930,30 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Arbets-Excel – inte master</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Taxa_Förslag</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ingår för föreslagna saknade taxekoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Regelspårning</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ingår för spårbarhet</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -8889,7 +8977,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Excel Builder v2.0.0-alpha.1</t>
+          <t>Excel Builder</t>
         </is>
       </c>
     </row>
@@ -8916,33 +9004,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nästa steg:</t>
+          <t>Taxa_Förslag och Regelspårning ingår i alla genererade arbetsböcker.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>1. Koppla mot befintlig Arbets-Excel/EDP-data.</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2. Behåll befintliga EDP-koder där matchning är säker.</t>
+          <t>Nästa steg:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3. Markera osäkra rader för manuell kontroll.</t>
+          <t>1. Koppla mot befintlig Arbets-Excel/EDP-data.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Behåll befintliga EDP-koder där matchning är säker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Markera osäkra rader för manuell kontroll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>4. Skapa ny godkänd arbetsversion.</t>
         </is>
@@ -8951,4 +9049,311 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Taxa_Förslag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Förslag på saknade taxekoder. Förslag ska granskas innan import till EDP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Parseroutput</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Paragraf</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Taxapunkt</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Enhet</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Föreslagen taxekod</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Föreslagen benämning</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Säkerhet</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>EDP Standardtaxor / regelverk / manuell granskning</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>EDP-data får aldrig blandas mellan projekt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Regelspårning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Spårar hur varje rad/fält byggdes: Word, EDP, standardtaxor eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Parseroutput</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Paragraf</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Taxapunkt</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Fält</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Värde</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Ursprung</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Regel</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Taxakod</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Ej satt</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Taxakod får endast sättas från säker EDP-match eller markerat förslag.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Regelverk</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Standardflik för framtida spårning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sammanfattning" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_Förslag" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Avviker_Standard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxepunkter'!$A$1:$J$242</definedName>
@@ -205,7 +206,28 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EdpAvvikerStandardTable" displayName="EdpAvvikerStandardTable" ref="A6:L7" headerRowCount="1">
+  <autoFilter ref="A6:L7"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="EDP taxekod"/>
+    <tableColumn id="3" name="EDP benämning"/>
+    <tableColumn id="4" name="EDP faktor"/>
+    <tableColumn id="5" name="EDP taxedel"/>
+    <tableColumn id="6" name="Standard taxekod"/>
+    <tableColumn id="7" name="Standard benämning"/>
+    <tableColumn id="8" name="Standard faktor"/>
+    <tableColumn id="9" name="Standard taxedel"/>
+    <tableColumn id="10" name="Avvikelse"/>
+    <tableColumn id="11" name="Rekommendation"/>
+    <tableColumn id="12" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
   <autoFilter ref="A6:J7"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Kommun"/>
@@ -9208,6 +9230,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>EDP Export avviker från standardtaxa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Visar avvikelser mot standardtaxor. Befintlig Taxa_från_edp är fast och ändras aldrig automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Parseroutput</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>EDP taxekod</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>EDP benämning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>EDP faktor</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>EDP taxedel</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Standard taxekod</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Standard benämning</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Standard faktor</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Standard taxedel</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Avvikelse</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Rekommendation</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Granska manuellt. Ändra inte befintlig EDP automatiskt.</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9217,7 +9393,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
@@ -9331,7 +9507,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Taxakod får endast sättas från säker EDP-match eller markerat förslag.</t>
+          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">

--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -607,26 +607,21 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>En- och tvåbostadshus</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>1 650,00 kr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -639,26 +634,21 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Fritidshus</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -671,26 +661,21 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Verksamhet</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -703,13 +688,11 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Lägenhet i flerbostadshus</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>lägenhet</t>
@@ -720,13 +703,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -739,13 +720,11 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Lägenhet för specialändamål</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>lägenhet</t>
@@ -756,13 +735,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -775,26 +752,21 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Anläggning</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -807,26 +779,21 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Säsongsbaserad uppställningsplats</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -839,13 +806,11 @@
           <t>2.1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Campingstuga/-lägenhet</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>lägenhet</t>
@@ -856,13 +821,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -875,13 +838,11 @@
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -892,13 +853,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -911,26 +870,21 @@
           <t>2.2.1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Extrakärl 190 l (restavfall)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -943,13 +897,11 @@
           <t>2.2.2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -960,13 +912,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -979,26 +929,21 @@
           <t>2.2.2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Extrakärl 190 l (restavfall)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1011,26 +956,21 @@
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Gemensam uppsamlingsplats för mat-/restavfall</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1043,26 +983,21 @@
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Extra digital licens (årskostnad)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1075,26 +1010,21 @@
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Fysisk nyckel, kallad fob (engångskostnad)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1107,26 +1037,21 @@
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Byte av telefonnummer kopplat till licens</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1139,26 +1064,21 @@
           <t>2.2.3</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Kostnad för öppning av behållare</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1171,13 +1091,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1188,13 +1106,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1207,13 +1123,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1224,13 +1138,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1243,13 +1155,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1260,13 +1170,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1279,13 +1187,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1296,13 +1202,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1315,13 +1219,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Kärl 190 l (förpackningar)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1332,13 +1234,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1351,13 +1251,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>Kärl 370 l (förpackningar)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1368,13 +1266,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1387,13 +1283,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Kärl 660 l (förpackningar)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1404,13 +1298,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1423,13 +1315,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Kärl 190 l (tidningar och returpapper)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1440,13 +1330,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1459,13 +1347,11 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>Kärl 370 l (tidningar och returpapper)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1476,13 +1362,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1495,26 +1379,21 @@
           <t>2.2.4</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>(mat-/restavfall, förpackningar)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1527,13 +1406,11 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1544,13 +1421,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1563,13 +1438,11 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1580,13 +1453,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1599,13 +1470,11 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1616,13 +1485,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1635,13 +1502,11 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1652,13 +1517,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1671,26 +1534,21 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>Bottentömmande behållare (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1703,26 +1561,21 @@
           <t>2.2.5</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>Lastväxlarflak (restavfall)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1735,13 +1588,11 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1752,13 +1603,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1771,13 +1620,11 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1788,13 +1635,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1807,13 +1652,11 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1824,13 +1667,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1843,13 +1684,11 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1860,13 +1699,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1879,26 +1716,21 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>Bottentömmande behållare (mat-/restavfall)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1911,26 +1743,21 @@
           <t>2.2.6</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>Lastväxlarflak (restavfall)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1943,13 +1770,11 @@
           <t>2.2.7</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>Kärl 140 l (kontors-/returpapper)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -1960,13 +1785,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -1979,26 +1802,21 @@
           <t>2.2.7</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>Egen överlämning av förbrukat kontors-/returpapper enligt anvisning</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2011,26 +1829,21 @@
           <t>2.2.7</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>Egen överlämning av förbrukat matfett enligt anvisning</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2043,26 +1856,21 @@
           <t>2.3</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2075,26 +1883,21 @@
           <t>2.3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2107,13 +1910,11 @@
           <t>2.3</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Lyftavgift kärl</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2124,13 +1925,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2143,26 +1942,21 @@
           <t>2.4.1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>Fakturavgift</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2175,13 +1969,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>Delat kärl 240 l matavfall 40 kg</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2192,13 +1984,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2211,13 +2001,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>Delat kärl 240 l restavfall 40 kg</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2228,13 +2016,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2247,13 +2033,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>Extra kärl 140 l matavfall 60 kg</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2264,13 +2048,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2283,13 +2065,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>Extra kärl 140-190 l restavfall 60 kg</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2300,13 +2080,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2319,13 +2097,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>Kärl 370 l restavfall 60 kg</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2336,13 +2112,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2355,13 +2129,11 @@
           <t>2.4.2</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>Kärl 660 l restavfall 100 kg</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -2372,13 +2144,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2391,13 +2161,11 @@
           <t>2.4.3</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>Överfullt kärl</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2408,13 +2176,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2427,26 +2193,21 @@
           <t>2.4.3</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>Överfull bottentömmande behållare</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2459,13 +2220,11 @@
           <t>2.4.4</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>Byte av trasigt kärl vid oaktsamhet</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2476,13 +2235,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2495,13 +2252,11 @@
           <t>2.4.5</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>Byte/återtag av kärl en (1) ggr/år 140–240 liter</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>liter</t>
@@ -2512,13 +2267,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2531,13 +2284,11 @@
           <t>2.4.5</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>Byte/återtag av kärl en (1) ggr/år 370–660 liter</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>liter</t>
@@ -2548,13 +2299,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2567,13 +2316,11 @@
           <t>2.4.5</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>Ytterligare byte av kärl under kalenderåret</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2584,13 +2331,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2603,13 +2348,11 @@
           <t>2.4.6</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>Kärl</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2620,13 +2363,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2639,26 +2380,21 @@
           <t>2.4.6</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>Bottentömmande behållare</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2671,13 +2407,11 @@
           <t>2.4.7</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>Kärl 140-660 L 1,5-10</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2688,13 +2422,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2707,13 +2439,11 @@
           <t>2.4.7</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>Kärl 140-660 L 10-20</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2724,13 +2454,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2743,13 +2471,11 @@
           <t>2.4.7</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>Kärl 140-660 L 20-30</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2760,13 +2486,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2779,26 +2503,21 @@
           <t>2.4.7</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>Avfallsport/dörr</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2811,26 +2530,21 @@
           <t>2.4.7</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>Låst dörr, med kod</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2843,13 +2557,11 @@
           <t>2.4.8</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>Kärl 140 l matavfall</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2860,13 +2572,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2879,13 +2589,11 @@
           <t>2.4.8</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>Kärl 190 l restavfall</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2896,13 +2604,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2915,13 +2621,11 @@
           <t>2.4.8</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>Kärl 370 l restavfall</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2932,13 +2636,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2951,13 +2653,11 @@
           <t>2.4.8</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>Kärl 660 l restavfall</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -2968,13 +2668,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -2987,26 +2685,21 @@
           <t>2.4.8</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>Bottentömmande behållare</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3019,26 +2712,21 @@
           <t>2.4.9</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>Sidlastande fordon</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3051,26 +2739,21 @@
           <t>2.4.9</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>Bottentömmande fordon</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3083,26 +2766,21 @@
           <t>2.4.9</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>Tömningsavgift per behållare</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3115,26 +2793,21 @@
           <t>2.4.10</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>Betalsäck</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3147,26 +2820,21 @@
           <t>2.4.10</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>Akutsäck</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3179,26 +2847,21 @@
           <t>2.4.11</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>Matavfallspåsar 9 L</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3211,26 +2874,21 @@
           <t>2.4.11</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>Matavfallspåsar 22 L</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3243,13 +2901,11 @@
           <t>2.4.11</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>Gravitationslås till kärl</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>kärl</t>
@@ -3260,13 +2916,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3279,26 +2933,21 @@
           <t>2.4.11</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>Extra nyckel till gravitationslås</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3311,26 +2960,21 @@
           <t>2.5.1</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>Kommunalt avfall</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3343,26 +2987,21 @@
           <t>2.5.1</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>Farligt avfall (ej uppmärkt)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3375,26 +3014,21 @@
           <t>2.5.1</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>Farligt avfall (uppmärkt)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3407,26 +3041,21 @@
           <t>2.5.1</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>Avisering av ankomst</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3439,13 +3068,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>Upp till 3 m3</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3456,13 +3083,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3475,13 +3100,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>Mellan 3 m3 och 6 m3</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3492,13 +3115,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3511,13 +3132,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>Mellan 6 m3 och 9 m3</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3528,13 +3147,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3547,13 +3164,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>Tillägg per m3 över 9 m3</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3564,13 +3179,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3583,13 +3196,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>Bad-, disk- och tvättbrunn upp till 3 m3</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3600,13 +3211,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3619,13 +3228,11 @@
           <t>3.1</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>Tillägg per m3 över 3 m3</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3636,13 +3243,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3655,26 +3260,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 5-25 m</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3687,26 +3287,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 25-35 m</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3719,26 +3314,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 36-45 m</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3751,26 +3341,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 46-55 m</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3783,13 +3368,11 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>Hantering av brunnslock som väger 15-25 kg</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -3800,13 +3383,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3819,26 +3400,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>Krav på information om tömningstid</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3851,26 +3427,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>Krav på närvaro vid specificerad tömningstid</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3883,26 +3454,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>Hantering av kod för kodlås vid slamtömning</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3915,26 +3481,21 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>Hetvattentvätt med spolbil, timersättning</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3947,13 +3508,11 @@
           <t>3.2</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>Tömning av extra tank/brunn i samband med ordinarie/budad tömning upp till 5 m3</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>m³</t>
@@ -3964,13 +3523,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -3983,26 +3540,21 @@
           <t>3.3</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4015,26 +3567,21 @@
           <t>3.3</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>Budning utanför ordinarie tömningsperiod (1 nov – 30 april)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4047,13 +3594,11 @@
           <t>3.3</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>Tömning av toalettvagnar eller liknande /styck</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>styck</t>
@@ -4064,13 +3609,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4083,13 +3626,11 @@
           <t>3.4</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>Latrinbehållare 37 liter inkl. mottagning och behandling</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>liter</t>
@@ -4100,13 +3641,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4119,13 +3658,11 @@
           <t>4.1</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>Filtermassor upp till 500 kg</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -4136,13 +3673,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4155,13 +3690,11 @@
           <t>4.1</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>Filtermassor 500-1000 kg</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -4172,13 +3705,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4191,26 +3722,21 @@
           <t>4.2</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>Krav på information om hämtningstid</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4223,26 +3749,21 @@
           <t>4.2</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>Krav på närvaro vid specificerad hämtningstid</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4255,26 +3776,21 @@
           <t>4.2</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>Hantering av kod för kodlås</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4287,13 +3803,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>Upp till 3 m3</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4304,13 +3818,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4323,13 +3835,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>Mellan 3 m3 och 6 m3</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4340,13 +3850,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4359,13 +3867,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
           <t>Över 6 m3</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4376,13 +3882,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4395,26 +3899,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 5-25 m</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4427,26 +3926,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 25-35 m</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4459,26 +3953,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 36-45 m</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4491,26 +3980,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
           <t>Dragning av extra slang vid 46-55 m</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4523,13 +4007,11 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>Hantering av brunnslock som väger 15-25 kg</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -4540,13 +4022,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4559,26 +4039,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>Krav på information om tömningstid</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4591,26 +4066,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>Krav på närvaro vid specificerad tömningstid</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4623,13 +4093,11 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>Hantering av kod för kodlås vid tömning</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>tömning</t>
@@ -4640,13 +4108,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4659,26 +4125,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>Hetvattentvätt med spolbil, timersättning</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4691,26 +4152,21 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
           <t>Silikontätning per lock</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4723,13 +4179,11 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>Tömning av extra tank i samband med ordinarie/budad tömning upp till 5 m3</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>m³</t>
@@ -4740,13 +4194,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4759,26 +4211,21 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4791,26 +4238,21 @@
           <t>5.3</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>Budning utanför ordinarie tömningsperiod</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4823,26 +4265,21 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>Verksamheter</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4855,26 +4292,21 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>Övriga abonnemangstyper</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4887,26 +4319,21 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>Vågkort</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4919,26 +4346,21 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t>Borttappat vågkort</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4951,13 +4373,11 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>Ej redovisad ankomst till ÅVC (för företagare och privatpersoner som lämnar verksamhetsavfall utan att anmäla sin ankomst)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>besök</t>
@@ -4968,13 +4388,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -4987,13 +4405,11 @@
           <t>6.1.1</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>Ej redovisad eller fel redovisad fraktion av avfall</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>fraktion</t>
@@ -5004,13 +4420,11 @@
           <t>XXXX kr</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5023,26 +4437,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>Avfall till energiåtervinning (240 L sopsäck)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>styck</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5055,26 +4464,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>Avfall till energiåtervinning</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5087,26 +4491,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>Skrymmande avfall till energiåtervinning större än 20×20×80</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5119,26 +4518,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>Träavfall – obehandlat, utan tapet, plastmatta, tjärpapp</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5151,26 +4545,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>Träavfall – behandlat, utan tapet, plastmatta, tjärpapp</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5183,26 +4572,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>Tryckimpregnerat virke, pall</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5215,26 +4599,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>Betong, lättbetong</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5247,26 +4626,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>Gips, gipsskivor</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5279,26 +4653,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>Tegel</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5311,26 +4680,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>Fönster- och planglas utan karm</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5343,22 +4707,16 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>Fönster med karm</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5371,26 +4729,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>Plast</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5403,26 +4756,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>Isolering utan innehåll av asbest</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5435,26 +4783,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>Klinker, keramik, porslin</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5467,26 +4810,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>Handfat</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>styck</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5499,26 +4837,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
           <t>WC-stol</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>styck</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5531,26 +4864,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
           <t>Metall</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5563,26 +4891,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
           <t>Textilier</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5595,26 +4918,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>Fiskeredskap</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5627,26 +4945,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>Ätbart fett/frityrolja</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>liter</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5659,26 +4972,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>Kvistar och grenar</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5691,22 +4999,16 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>Jord</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5719,22 +5021,16 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>Sten</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5747,22 +5043,16 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>Stubbar/rötter för krossning</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5775,26 +5065,21 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
           <t>Flera fraktioner för egen sortering på ramp (max 2 m³)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5807,22 +5092,16 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>Osorterat avfall till sortering (ej innehåll av farligt avfall och elavfall)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5835,13 +5114,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>Tonerkassetter, utan elektronik/chip</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -5852,13 +5129,11 @@
           <t>31,88</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5871,13 +5146,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>Oljeemulsion, emballerat</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -5888,13 +5161,11 @@
           <t>20,81</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5907,13 +5178,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>Förorenad olja innehållande PCB</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -5924,13 +5193,11 @@
           <t>38,25</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5943,13 +5210,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>Oljeavskiljarslam</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -5960,13 +5225,11 @@
           <t>6,56</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -5979,13 +5242,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>Diesel</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -5996,13 +5257,11 @@
           <t>21,94</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6015,13 +5274,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>Bensinrester</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6032,13 +5289,11 @@
           <t>21,94</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6051,13 +5306,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>Hydralslang, med/utan koppling</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6068,13 +5321,11 @@
           <t>33,94</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6087,13 +5338,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>Förpackningar, tömde ej rengjorda</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6104,13 +5353,11 @@
           <t>25,50</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6123,13 +5370,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>Oljeavfall, fast osorterat emba</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6140,13 +5385,11 @@
           <t>23,44</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6159,13 +5402,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>Absorbermedel, filtermaterial</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6176,13 +5417,11 @@
           <t>15,38</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6195,13 +5434,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>Oljefilter</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6212,13 +5449,11 @@
           <t>15,38</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6231,13 +5466,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
           <t>Bromsvätska</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6248,13 +5481,11 @@
           <t>11,44</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6267,13 +5498,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
           <t>Transformator, kondensator med PCB</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6284,13 +5513,11 @@
           <t>84,94</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6303,13 +5530,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>Fogskum</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6320,13 +5545,11 @@
           <t>90,00</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6339,13 +5562,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>Halon</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6356,13 +5577,11 @@
           <t>127,50</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6375,13 +5594,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>Koldioxid</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6392,13 +5609,11 @@
           <t>112,13</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6411,13 +5626,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>Brandsläckare</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6428,13 +5641,11 @@
           <t>91,69</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6447,13 +5658,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>Helium</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6464,13 +5673,11 @@
           <t>117,19</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6483,13 +5690,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>Tändare</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6500,13 +5705,11 @@
           <t>127,50</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6519,13 +5722,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>Syrgas</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6536,13 +5737,11 @@
           <t>117,19</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6555,13 +5754,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>Oxiderande fast ämne/vätska</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6572,13 +5769,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6591,13 +5786,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>Klorex</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6608,13 +5801,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6627,13 +5818,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>Aerosoler isocyanat, bekämpning</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6644,13 +5833,11 @@
           <t>101,06</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6663,13 +5850,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>Gasol inkl tub</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6680,13 +5865,11 @@
           <t>102,00</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6699,13 +5882,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>Gasol, blå programmet</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6716,13 +5897,11 @@
           <t>169,88</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6735,13 +5914,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>Giftig organisk vätska</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6752,13 +5929,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6771,13 +5946,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
       <c r="C184" t="inlineStr">
         <is>
           <t>Småkemikalier, ej Hg-haltiga</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6788,13 +5961,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6807,13 +5978,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
       <c r="C185" t="inlineStr">
         <is>
           <t>Giftig oorganisk vätska</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6824,13 +5993,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6843,13 +6010,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
           <t>Oxidationsmedel, flytande</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6860,13 +6025,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6879,13 +6042,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
           <t>Asbest, emballerat</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6896,13 +6057,11 @@
           <t>22,88</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6915,13 +6074,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>Smittförande avfall</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6932,13 +6089,11 @@
           <t>40,31</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6951,13 +6106,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
           <t>Lösningsmedel</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -6968,13 +6121,11 @@
           <t>20,63</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -6987,13 +6138,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr">
         <is>
           <t>Väteperoxid</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7004,13 +6153,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7023,13 +6170,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>Flourvätesyra</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7040,13 +6185,11 @@
           <t>81,38</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7059,13 +6202,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr">
         <is>
           <t>Svavelsyra</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7076,13 +6217,11 @@
           <t>81,38</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7095,13 +6234,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>Salpetersyra</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7112,13 +6249,11 @@
           <t>81,38</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7131,13 +6266,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
           <t>Surt oorganisk fast ämne</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7148,13 +6281,11 @@
           <t>103,31</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7167,13 +6298,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>Surt organisk fast ämne</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7184,13 +6313,11 @@
           <t>127,50</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7203,13 +6330,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
           <t>Surt oorganisk vätska</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7220,13 +6345,11 @@
           <t>127,50</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7239,13 +6362,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>Surt organisk vätska</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7256,13 +6377,11 @@
           <t>127,50</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7275,13 +6394,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
       <c r="C198" t="inlineStr">
         <is>
           <t>Ammoniaklösning</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7292,13 +6409,11 @@
           <t>63,38</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7311,13 +6426,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
           <t>Alkaliskt avfall fast</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7328,13 +6441,11 @@
           <t>27,75</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7347,13 +6458,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr">
         <is>
           <t>Basiskt organiskt fast/flytande</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7364,13 +6473,11 @@
           <t>46,50</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7383,13 +6490,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
           <t>Fotokemikalier</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7400,13 +6505,11 @@
           <t>38,25</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7419,13 +6522,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr">
         <is>
           <t>Bekämpningsmedel aerosoler</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7436,13 +6537,11 @@
           <t>73,69</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7455,13 +6554,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr">
         <is>
           <t>Bekämpningsmedel fast</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7472,13 +6569,11 @@
           <t>85,88</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7491,13 +6586,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
           <t>Bekämpningsmedel flytande</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7508,13 +6601,11 @@
           <t>61,69</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7527,13 +6618,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
           <t>Kvicksilverhaltigt avfall</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7544,13 +6633,11 @@
           <t>1 034,81</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7563,13 +6650,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
           <t>Kvicksilver i föremål</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7580,13 +6665,11 @@
           <t>1 034,81</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7599,13 +6682,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
           <t>Oljehaltigt avfall (ej PCB)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>liter</t>
@@ -7616,13 +6697,11 @@
           <t>15,94</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7635,13 +6714,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>Olja förorenad (ej PCB)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>liter</t>
@@ -7652,13 +6729,11 @@
           <t>23,44</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7671,13 +6746,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
           <t>Färg-, lack-, limburkar lösning</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7688,13 +6761,11 @@
           <t>19,88</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7707,13 +6778,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
           <t>Färg-, lack-, limburkar lösning aerosoler</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7724,13 +6793,11 @@
           <t>43,31</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7743,13 +6810,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
           <t>Isocyanater</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7760,13 +6825,11 @@
           <t>103,88</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7779,13 +6842,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>Härdare metyl- etylketonperoxid</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7796,13 +6857,11 @@
           <t>109,88</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7815,13 +6874,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
           <t>Härdare dibenzoylperoxid</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7832,13 +6889,11 @@
           <t>114,38</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7851,13 +6906,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
           <t>Färg-,lack-, limburkar vattenbaserade</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7868,13 +6921,11 @@
           <t>15,38</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7887,13 +6938,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
           <t>Tensida alkaliska flytande avfall</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7904,13 +6953,11 @@
           <t>25,50</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7923,13 +6970,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
           <t>Rengöring/vaskmedel fast</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7940,13 +6985,11 @@
           <t>27,19</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7959,13 +7002,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
           <t>Alkaliska flytande avfall</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -7976,13 +7017,11 @@
           <t>27,75</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -7995,13 +7034,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
           <t>Cytotoxiska läkemedel, cytostat</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8012,13 +7049,11 @@
           <t>64,88</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8031,13 +7066,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
           <t>Rökdetektor med andra isotoper</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8048,13 +7081,11 @@
           <t>1 911,75</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8067,13 +7098,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
           <t>Rökdetektor med Am 241</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8084,13 +7113,11 @@
           <t>1 911,75</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8103,13 +7130,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
           <t>Batterier stav, pencell</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8120,13 +7145,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8139,13 +7162,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
           <t>Batterier lithium</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8156,13 +7177,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8175,13 +7194,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
           <t>Bil-, mcbatteri med bly</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>styck</t>
@@ -8192,13 +7209,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8211,13 +7226,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
           <t>Glödlampor</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8228,13 +7241,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8247,13 +7258,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
           <t>Lysrör</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8264,13 +7273,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8283,13 +7290,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr">
         <is>
           <t>Elavfall, små elektronik</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8300,13 +7305,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8319,13 +7322,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr">
         <is>
           <t>El-avfall fast installation</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8336,13 +7337,11 @@
           <t>37,60</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8355,13 +7354,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
       <c r="C228" t="inlineStr">
         <is>
           <t>El-avfall kabel</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8372,13 +7369,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8391,13 +7386,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
           <t>Toner, färgpatron med elektronik</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8408,13 +7401,11 @@
           <t>37,60</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8427,13 +7418,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
           <t>Tv, radio, skärm, skrivare utan färgpatron</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8444,13 +7433,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8463,13 +7450,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
       <c r="C231" t="inlineStr">
         <is>
           <t>Kyl-, frysskåp, -box</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>styck</t>
@@ -8480,13 +7465,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8499,13 +7482,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
       <c r="C232" t="inlineStr">
         <is>
           <t>Kyl-, frysskåp, -box från verksamhet</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8516,13 +7497,11 @@
           <t>37,60</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8535,13 +7514,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr">
         <is>
           <t>Spis, tvätt-, diskmaskin</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>styck</t>
@@ -8552,13 +7529,11 @@
           <t>0,00</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8571,13 +7546,11 @@
           <t>6.1.2</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
           <t>Spis, tvätt-, diskmaskin från verksamhet</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
           <t>kilogram</t>
@@ -8588,13 +7561,11 @@
           <t>37,60</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8607,13 +7578,11 @@
           <t>6.1.3</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr">
         <is>
           <t>Container X m3</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>m³</t>
@@ -8624,13 +7593,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8643,13 +7610,11 @@
           <t>6.1.3</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
       <c r="C236" t="inlineStr">
         <is>
           <t>Container X m3</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>m³</t>
@@ -8660,13 +7625,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8679,13 +7642,11 @@
           <t>6.1.3</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr">
         <is>
           <t>Container X m3</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
           <t>m³</t>
@@ -8696,13 +7657,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8715,13 +7674,11 @@
           <t>6.1.3</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>Omklassning av felsorterad container</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>container</t>
@@ -8732,13 +7689,11 @@
           <t>XX kr</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8751,13 +7706,11 @@
           <t>6.1.4</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
           <t>Okänt farligt avfall (säkerhetsdatablad saknas)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>fraktion</t>
@@ -8768,13 +7721,11 @@
           <t>XXX kr</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8787,13 +7738,11 @@
           <t>6.1.4</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
           <t>Ombud för rapportering av farligt avfall i Avfallsregistret</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>tillfälle</t>
@@ -8804,13 +7753,11 @@
           <t>XXX kr</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8823,13 +7770,11 @@
           <t>6.1.4</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr">
         <is>
           <t>Administrativ rapporteringsavgift till Avfallsregistret</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
           <t>tillfälle</t>
@@ -8840,13 +7785,11 @@
           <t>XXX kr</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -8859,13 +7802,11 @@
           <t>6.1.4</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>Ombud för registrering av El-kretsen avlämnarintyg i Hämtplatsportalen</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
           <t>tillfälle</t>
@@ -8876,13 +7817,11 @@
           <t>XXX kr</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>Ej kopplad</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>parser3_result.json</t>
@@ -9003,9 +7942,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -9020,9 +7957,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -9030,9 +7965,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -9079,7 +8012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9188,31 +8121,6 @@
       <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>EDP Standardtaxor / regelverk / manuell granskning</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>EDP-data får aldrig blandas mellan projekt.</t>
         </is>
       </c>
     </row>
@@ -9384,7 +8292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9490,42 +8398,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Taxakod</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Ej satt</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Regelverk</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Standardflik för framtida spårning.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -23784,7 +23784,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>tvåbostadshus</t>
+          <t>en-och, tvåbostadshus</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -24097,7 +24097,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>campingstuga, lägenhet</t>
+          <t>-lägenhet, campingstuga, lägenhet</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
@@ -24190,7 +24190,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -24372,7 +24372,7 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>gemensam, mat, restavfall, uppsamlingsplats</t>
+          <t>gemensam, mat-, restavfall, uppsamlingsplats</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -24404,17 +24404,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -24424,7 +24420,7 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -24452,20 +24448,12 @@
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Tillfälle</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>TILLFÄLLE</t>
-        </is>
-      </c>
+      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -24475,7 +24463,7 @@
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>Avfallstyp kunde inte härledas.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24607,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
@@ -25134,7 +25122,7 @@
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>förpackningar, mat, restavfall</t>
+          <t>förpackningar, mat-, restavfall</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -25197,7 +25185,7 @@
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
@@ -25417,7 +25405,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>behållare, bottentömmande, mat, restavfall</t>
+          <t>behållare, bottentömmande, mat-, restavfall</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -25527,7 +25515,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
@@ -25747,7 +25735,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>behållare, bottentömmande, mat, restavfall</t>
+          <t>behållare, bottentömmande, mat-, restavfall</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -25853,7 +25841,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>140, kontors, kärl, returpapper</t>
+          <t>140, kontors-, kärl, returpapper</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -25896,7 +25884,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>anvisning, egen, enligt, förbrukat, kontors, returpapper, överlämning</t>
+          <t>anvisning, egen, enligt, förbrukat, kontors-, returpapper, överlämning</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -26279,7 +26267,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Matavfall</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -26338,7 +26326,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -26363,7 +26351,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>140, 190, extra, kilogram, kärl, restavfall</t>
+          <t>140-190, extra, kilogram, kärl, restavfall</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
@@ -26603,17 +26591,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr"/>
       <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -26623,7 +26607,7 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -26677,7 +26661,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>140, 240, byte, ggr, kärl, liter, återtag</t>
+          <t>140-240, byte, ggr, kärl, liter, återtag</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -26736,7 +26720,7 @@
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>370, 660, byte, ggr, kärl, liter, återtag</t>
+          <t>370-660, byte, ggr, kärl, liter, återtag</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -26932,7 +26916,7 @@
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>140-660, 5-10, kärl</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -26991,7 +26975,7 @@
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>10-20, 140-660, kärl</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -27050,7 +27034,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>140-660, 20-30, kärl</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -27662,11 +27646,7 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Matavfall</t>
-        </is>
-      </c>
+      <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -27680,7 +27660,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -27688,7 +27668,11 @@
           <t>matavfallspåsar</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -27713,11 +27697,7 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Matavfall</t>
-        </is>
-      </c>
+      <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -27735,7 +27715,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -27743,7 +27723,11 @@
           <t>matavfallspåsar</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr"/>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -27815,17 +27799,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G84" s="6" t="inlineStr"/>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr"/>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -27835,7 +27815,7 @@
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -28285,7 +28265,7 @@
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>bad, disk, tvättbrunn, upp</t>
+          <t>bad-, disk-och, tvättbrunn, upp</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -28372,27 +28352,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G95" s="6" t="inlineStr"/>
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr"/>
       <c r="J95" s="6" t="inlineStr"/>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>5-25, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -28419,27 +28395,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G96" s="6" t="inlineStr"/>
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="6" t="inlineStr"/>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>25-35, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -28466,27 +28438,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G97" s="6" t="inlineStr"/>
       <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="6" t="inlineStr"/>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>36-45, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -28513,27 +28481,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G98" s="6" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="6" t="inlineStr"/>
       <c r="J98" s="6" t="inlineStr"/>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>46-55, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -28583,7 +28547,7 @@
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>brunnslock, hantering, kilogram, som, väger</t>
+          <t>15-25, brunnslock, hantering, kilogram, som, väger</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr">
@@ -28795,11 +28759,7 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G104" s="6" t="inlineStr"/>
       <c r="H104" s="6" t="inlineStr">
         <is>
           <t>Volym</t>
@@ -28813,7 +28773,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
@@ -28821,7 +28781,11 @@
           <t>brunn, budad, extra, ordinarie, samband, tank, tömning, upp</t>
         </is>
       </c>
-      <c r="M104" s="6" t="inlineStr"/>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -28857,7 +28821,7 @@
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>budning, inom, maj, oktober, ordinarie, tömningsperiod</t>
+          <t>budning, inom, maj-31, oktober, ordinarie, tömningsperiod</t>
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr">
@@ -28900,7 +28864,7 @@
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>april, budning, nov, ordinarie, tömningsperiod, utanför</t>
+          <t>april, budning, nov-30, ordinarie, tömningsperiod, utanför</t>
         </is>
       </c>
       <c r="M106" s="6" t="inlineStr">
@@ -29124,7 +29088,7 @@
       </c>
       <c r="L110" s="6" t="inlineStr">
         <is>
-          <t>1000, 500, filtermassor, kilogram</t>
+          <t>500-1000, filtermassor, kilogram</t>
         </is>
       </c>
       <c r="M110" s="6" t="inlineStr">
@@ -29450,27 +29414,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G117" s="6" t="inlineStr"/>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="6" t="inlineStr"/>
       <c r="J117" s="6" t="inlineStr"/>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>5-25, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -29497,27 +29457,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="6" t="inlineStr"/>
       <c r="J118" s="6" t="inlineStr"/>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>25-35, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -29544,27 +29500,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G119" s="6" t="inlineStr"/>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="6" t="inlineStr"/>
       <c r="J119" s="6" t="inlineStr"/>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>36-45, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -29591,27 +29543,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G120" s="6" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="6" t="inlineStr"/>
       <c r="J120" s="6" t="inlineStr"/>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>46-55, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -29661,7 +29609,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>brunnslock, hantering, kilogram, som, väger</t>
+          <t>15-25, brunnslock, hantering, kilogram, som, väger</t>
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr">
@@ -29916,11 +29864,7 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G127" s="6" t="inlineStr"/>
       <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Volym</t>
@@ -29934,7 +29878,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
@@ -29942,7 +29886,11 @@
           <t>budad, extra, ordinarie, samband, tank, tömning, upp</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr"/>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -29978,7 +29926,7 @@
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>budning, inom, maj, oktober, ordinarie, tömningsperiod</t>
+          <t>budning, inom, maj-31, oktober, ordinarie, tömningsperiod</t>
         </is>
       </c>
       <c r="M128" s="6" t="inlineStr">
@@ -30492,11 +30440,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -30510,15 +30454,19 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>kilogram, obehandlat, plastmatta, tapet, tjärpapp, träavfall</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="inlineStr"/>
+          <t>kilogram, plastmatta, tapet, tjärpapp, träavfall-obehandlat</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -30547,11 +30495,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G140" s="6" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -30565,15 +30509,19 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>behandlat, kilogram, plastmatta, tapet, tjärpapp, träavfall</t>
-        </is>
-      </c>
-      <c r="M140" s="6" t="inlineStr"/>
+          <t>kilogram, plastmatta, tapet, tjärpapp, träavfall-behandlat</t>
+        </is>
+      </c>
+      <c r="M140" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -30841,7 +30789,7 @@
       </c>
       <c r="L145" s="6" t="inlineStr">
         <is>
-          <t>fönster, karm, kilogram, planglas</t>
+          <t>fönster-och, karm, kilogram, planglas</t>
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr">
@@ -31159,7 +31107,7 @@
       </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
-          <t>stol, styck</t>
+          <t>styck, wc-stol</t>
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr">
@@ -31652,7 +31600,7 @@
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>Farligt avfall</t>
+          <t>Elavfall</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr"/>
@@ -31811,7 +31759,11 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Oljeavfall</t>
+        </is>
+      </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -31825,7 +31777,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr">
@@ -31833,11 +31785,7 @@
           <t>förorenad, innehållande, kilogram, olja, pcb</t>
         </is>
       </c>
-      <c r="M164" s="6" t="inlineStr">
-        <is>
-          <t>Avfallstyp kunde inte härledas.</t>
-        </is>
-      </c>
+      <c r="M164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -32361,11 +32309,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G174" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G174" s="6" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -32379,7 +32323,7 @@
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr">
@@ -32387,7 +32331,11 @@
           <t>kilogram, kondensator, pcb, transformator</t>
         </is>
       </c>
-      <c r="M174" s="6" t="inlineStr"/>
+      <c r="M174" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -33150,7 +33098,7 @@
       </c>
       <c r="L188" s="6" t="inlineStr">
         <is>
-          <t>haltiga, kilogram, småkemikalier</t>
+          <t>hg-haltiga, kilogram, småkemikalier</t>
         </is>
       </c>
       <c r="M188" s="6" t="inlineStr">
@@ -34451,7 +34399,11 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G212" s="6" t="inlineStr"/>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>Oljeavfall</t>
+        </is>
+      </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -34465,7 +34417,7 @@
       </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="L212" s="6" t="inlineStr">
@@ -34473,11 +34425,7 @@
           <t>förorenad, liter, olja, pcb</t>
         </is>
       </c>
-      <c r="M212" s="6" t="inlineStr">
-        <is>
-          <t>Avfallstyp kunde inte härledas.</t>
-        </is>
-      </c>
+      <c r="M212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -34525,7 +34473,7 @@
       </c>
       <c r="L213" s="6" t="inlineStr">
         <is>
-          <t>färg, kilogram, lack, limburkar, lösning</t>
+          <t>färg-, kilogram, lack-, limburkar, lösning</t>
         </is>
       </c>
       <c r="M213" s="6" t="inlineStr">
@@ -34580,7 +34528,7 @@
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>aerosoler, färg, kilogram, lack, limburkar, lösning</t>
+          <t>aerosoler, färg-, kilogram, lack-, limburkar, lösning</t>
         </is>
       </c>
       <c r="M214" s="6" t="inlineStr">
@@ -34690,7 +34638,7 @@
       </c>
       <c r="L216" s="6" t="inlineStr">
         <is>
-          <t>etylketonperoxid, härdare, kilogram, metyl</t>
+          <t>härdare, kilogram, metyl-etylketonperoxid</t>
         </is>
       </c>
       <c r="M216" s="6" t="inlineStr">
@@ -34800,7 +34748,7 @@
       </c>
       <c r="L218" s="6" t="inlineStr">
         <is>
-          <t>färg, kilogram, lack, limburkar, vattenbaserade</t>
+          <t>färg-, kilogram, lack-, limburkar, vattenbaserade</t>
         </is>
       </c>
       <c r="M218" s="6" t="inlineStr">
@@ -35276,11 +35224,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>Batterier</t>
-        </is>
-      </c>
+      <c r="G227" s="6" t="inlineStr"/>
       <c r="H227" s="6" t="inlineStr">
         <is>
           <t>Styck</t>
@@ -35294,15 +35238,19 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr">
         <is>
-          <t>bil, bly, mcbatteri, styck</t>
-        </is>
-      </c>
-      <c r="M227" s="6" t="inlineStr"/>
+          <t>bil-, bly, mcbatteri, styck</t>
+        </is>
+      </c>
+      <c r="M227" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -35519,7 +35467,7 @@
       </c>
       <c r="L231" s="6" t="inlineStr">
         <is>
-          <t>avfall, fast, installation, kilogram</t>
+          <t>el-avfall, fast, installation, kilogram</t>
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
@@ -35574,7 +35522,7 @@
       </c>
       <c r="L232" s="6" t="inlineStr">
         <is>
-          <t>avfall, kabel, kilogram</t>
+          <t>el-avfall, kabel, kilogram</t>
         </is>
       </c>
       <c r="M232" s="6" t="inlineStr"/>
@@ -35739,7 +35687,7 @@
       </c>
       <c r="L235" s="6" t="inlineStr">
         <is>
-          <t>boxstyck, frysskåp, kyl</t>
+          <t>-boxstyck, frysskåp, kyl-</t>
         </is>
       </c>
       <c r="M235" s="6" t="inlineStr"/>
@@ -35794,7 +35742,7 @@
       </c>
       <c r="L236" s="6" t="inlineStr">
         <is>
-          <t>boxfrån, frysskåp, kilogram, kyl, verksamhet</t>
+          <t>-boxfrån, frysskåp, kilogram, kyl-, verksamhet</t>
         </is>
       </c>
       <c r="M236" s="6" t="inlineStr"/>
@@ -35845,7 +35793,7 @@
       </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
-          <t>diskmaskin, spis, styck, tvätt</t>
+          <t>diskmaskin, spis, styck, tvätt-</t>
         </is>
       </c>
       <c r="M237" s="6" t="inlineStr">
@@ -35900,7 +35848,7 @@
       </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>diskmaskin, kilogram, spis, tvätt, verksamhet</t>
+          <t>diskmaskin, kilogram, spis, tvätt-, verksamhet</t>
         </is>
       </c>
       <c r="M238" s="6" t="inlineStr">
@@ -36254,11 +36202,7 @@
           <t>Verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G245" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G245" s="6" t="inlineStr"/>
       <c r="H245" s="6" t="inlineStr">
         <is>
           <t>Tillfälle</t>
@@ -36272,7 +36216,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr">
@@ -36280,7 +36224,11 @@
           <t>administrativ, avfallsregistret, rapporteringsavgift, tillfälle</t>
         </is>
       </c>
-      <c r="M245" s="6" t="inlineStr"/>
+      <c r="M245" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -36328,7 +36276,7 @@
       </c>
       <c r="L246" s="6" t="inlineStr">
         <is>
-          <t>avlämnarintyg, hämtplatsportalen, kretsen, ombud, registrering, tillfälle</t>
+          <t>avlämnarintyg, el-kretsen, hämtplatsportalen, ombud, registrering, tillfälle</t>
         </is>
       </c>
       <c r="M246" s="6" t="inlineStr">

--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -1462,17 +1462,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1650,17 +1650,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1927,17 +1927,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -1974,17 +1974,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2021,17 +2021,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2199,17 +2199,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2246,17 +2246,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2293,17 +2293,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -2963,17 +2963,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11775,6 +11775,852 @@
       <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Kommentar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Kärl 370 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KÄ370RE156</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 55</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kärl 660 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KÄ660RE156</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 65</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kärl 140 l (matavfall)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KÄ140MA156</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kärl 140 L, matavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 77</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Kärl 190 l (förpackningar)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KÄ190PLBUD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kärl 190 L, plastförpackningar. Budning</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 353</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Kärl 370 l (förpackningar)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KÄ370PLBUD</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, plastförpackningar. Budning</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 383</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.2.4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kärl 660 l (förpackningar)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>KÄ660PLBUD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, plastförpackningar. Budning</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 413</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.2.5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Kärl 370 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KÄ370RE156</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 55</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.2.5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kärl 660 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KÄ660RE156</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 65</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.2.5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kärl 140 l (matavfall)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KÄ140MA156</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kärl 140 L, matavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 77</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.2.6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Kärl 370 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KÄ370RE156</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 55</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.2.6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Kärl 660 l (restavfall)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KÄ660RE156</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 65</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.2.6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Kärl 140 l (matavfall)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KÄ140MA156</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Kärl 140 L, matavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 77</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kärl 370 l restavfall 60 kg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KÄ370RE52</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, restavfall. Varje vecka</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 57</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.604</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.77*0.35 | nyckelord=0.67*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.4.2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kärl 660 l restavfall 100 kg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KÄ660RE026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, restavfall. Var 14:e dag</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 68</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.78*0.35 | nyckelord=0.67*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.4.8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kärl 140 l matavfall</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>KÄ140MA156</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Kärl 140 L, matavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 77</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.664</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.75*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.4.8</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kärl 190 l restavfall</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KÄ190RE156</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Kärl 190 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 35</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.4.8</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kärl 370 l restavfall</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KÄ370RE156</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kärl 370 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 55</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.4.8</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kärl 660 l restavfall</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>kärl</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KÄ660RE156</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Kärl 660 L, restavfall. 3ggr/ vecka</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Standardtaxor: Standard Avfall rad 65</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
@@ -11946,7 +12792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:J265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12053,866 +12899,848 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>En- och tvåbostadshus</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ370RE156</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fritidshus</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ660RE156</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verksamhet</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ140MA156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lägenhet i flerbostadshus</t>
+          <t>Kärl 190 l (förpackningar)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ190PLBUD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 353</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lägenhet för specialändamål</t>
+          <t>Kärl 370 l (förpackningar)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ370PLBUD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 383</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anläggning</t>
+          <t>Kärl 660 l (förpackningar)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ660PLBUD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 413</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Säsongsbaserad uppställningsplats</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ370RE156</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 55</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Campingstuga/-lägenhet</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ660RE156</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 65</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kärl 240 l (mat-/restavfall)</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>KÄ140MA156</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 77</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.2.1</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Extrakärl 190 l (restavfall)</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>KÄ370RE156</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kärl 240 l (mat-/restavfall)</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>KÄ660RE156</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.74*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.2.2</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Extrakärl 190 l (restavfall)</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ140MA156</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 77</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.73*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gemensam uppsamlingsplats för mat-/restavfall</t>
+          <t>Kärl 370 l restavfall 60 kg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ370RE52</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.77*0.35 | nyckelord=0.67*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Extra digital licens (årskostnad)</t>
+          <t>Kärl 660 l restavfall 100 kg</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ660RE026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.78*0.35 | nyckelord=0.67*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fysisk nyckel, kallad fob (engångskostnad)</t>
+          <t>Kärl 140 l matavfall</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>KÄ140MA156</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Taxepunkter/Taxa_från_edp</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>EDP_MATCH</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.75*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Byte av telefonnummer kopplat till licens</t>
+          <t>Kärl 190 l restavfall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ190RE156</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.2.3</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kostnad för öppning av behållare</t>
+          <t>Kärl 370 l restavfall</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>KÄ370RE156</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kärl 240 l (mat-/restavfall)</t>
+          <t>Kärl 660 l restavfall</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Beslut</t>
+          <t>Taxakod</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>KÄ660RE156</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxa-förslag</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa får endast föreslås. Befintlig Taxa_från_edp ändras inte automatiskt.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TaxDecisionEngine</t>
+          <t>Standard Avfall rad 65</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Möjlig kunskapsbaserad standardträff. namn=0.76*0.35 | nyckelord=1.00*0.20 | avfallstyp=1.00*0.15 | faktor=0.00*0.15 | kategori=0.50*0.10 | enhet=0.00*0.05</t>
         </is>
       </c>
     </row>
@@ -12920,12 +13748,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kärl 370 l (restavfall)</t>
+          <t>En- och tvåbostadshus</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12935,17 +13763,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -12955,12 +13783,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -12968,12 +13796,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kärl 660 l (restavfall)</t>
+          <t>Fritidshus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12983,17 +13811,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13003,12 +13831,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13016,12 +13844,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kärl 140 l (matavfall)</t>
+          <t>Verksamhet</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -13031,17 +13859,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -13051,12 +13879,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13892,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kärl 190 l (förpackningar)</t>
+          <t>Lägenhet i flerbostadshus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -13079,17 +13907,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13099,12 +13927,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13112,12 +13940,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kärl 370 l (förpackningar)</t>
+          <t>Lägenhet för specialändamål</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -13127,17 +13955,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13147,12 +13975,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13160,12 +13988,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kärl 660 l (förpackningar)</t>
+          <t>Anläggning</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -13175,17 +14003,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -13195,12 +14023,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13208,12 +14036,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kärl 190 l (tidningar och returpapper)</t>
+          <t>Säsongsbaserad uppställningsplats</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -13223,17 +14051,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -13243,12 +14071,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13256,12 +14084,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kärl 370 l (tidningar och returpapper)</t>
+          <t>Campingstuga/-lägenhet</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -13271,17 +14099,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -13291,12 +14119,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13304,12 +14132,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.2.4</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(mat-/restavfall, förpackningar)</t>
+          <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -13352,12 +14180,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kärl 240 l (mat-/restavfall)</t>
+          <t>Extrakärl 190 l (restavfall)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13400,12 +14228,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kärl 370 l (restavfall)</t>
+          <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13448,12 +14276,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kärl 660 l (restavfall)</t>
+          <t>Extrakärl 190 l (restavfall)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -13463,17 +14291,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13483,12 +14311,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13496,12 +14324,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kärl 140 l (matavfall)</t>
+          <t>Gemensam uppsamlingsplats för mat-/restavfall</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -13511,17 +14339,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13531,12 +14359,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13544,12 +14372,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bottentömmande behållare (mat-/restavfall)</t>
+          <t>Extra digital licens (årskostnad)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -13559,17 +14387,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -13579,12 +14407,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13592,12 +14420,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.2.5</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lastväxlarflak (restavfall)</t>
+          <t>Fysisk nyckel, kallad fob (engångskostnad)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -13607,17 +14435,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Taxepunkter/Taxa_från_edp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Befintlig Taxakod i Taxepunkter behålls via paragraf+taxapunkt</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -13627,12 +14455,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>EDP_MATCH</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Variant/enhet skiljer eller saknas men kommun-EDP behålls.</t>
         </is>
       </c>
     </row>
@@ -13640,12 +14468,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kärl 240 l (mat-/restavfall)</t>
+          <t>Byte av telefonnummer kopplat till licens</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -13655,17 +14483,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -13675,12 +14503,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13688,12 +14516,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kärl 370 l (restavfall)</t>
+          <t>Kostnad för öppning av behållare</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -13703,17 +14531,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13723,12 +14551,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -13736,12 +14564,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kärl 660 l (restavfall)</t>
+          <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -13784,12 +14612,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kärl 140 l (matavfall)</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -13799,17 +14627,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -13819,12 +14647,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -13832,12 +14660,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bottentömmande behållare (mat-/restavfall)</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -13852,12 +14680,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13872,7 +14700,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -13880,12 +14708,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.2.6</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lastväxlarflak (restavfall)</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -13900,12 +14728,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13920,7 +14748,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -13928,12 +14756,12 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.2.7</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kärl 140 l (kontors-/returpapper)</t>
+          <t>Kärl 190 l (förpackningar)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -13948,12 +14776,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13968,7 +14796,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -13976,12 +14804,12 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.2.7</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Egen överlämning av förbrukat kontors-/returpapper enligt anvisning</t>
+          <t>Kärl 370 l (förpackningar)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -13991,17 +14819,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -14011,12 +14839,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14024,12 +14852,12 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.2.7</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egen överlämning av förbrukat matfett enligt anvisning</t>
+          <t>Kärl 660 l (förpackningar)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -14044,12 +14872,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14064,7 +14892,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14072,12 +14900,12 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Viktavgift matavfall</t>
+          <t>Kärl 190 l (tidningar och returpapper)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -14087,17 +14915,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14107,12 +14935,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -14120,12 +14948,12 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Viktavgift restavfall</t>
+          <t>Kärl 370 l (tidningar och returpapper)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -14135,17 +14963,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14155,12 +14983,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -14168,12 +14996,12 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2.4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lyftavgift kärl</t>
+          <t>(mat-/restavfall, förpackningar)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -14216,12 +15044,12 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.4.1</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fakturavgift</t>
+          <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -14264,12 +15092,12 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Delat kärl 240 l matavfall 40 kg</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -14279,17 +15107,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -14299,12 +15127,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14312,12 +15140,12 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Delat kärl 240 l restavfall 40 kg</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -14327,17 +15155,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -14347,12 +15175,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14360,12 +15188,12 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Extra kärl 140 l matavfall 60 kg</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -14375,17 +15203,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -14395,12 +15223,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14408,12 +15236,12 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Extra kärl 140-190 l restavfall 60 kg</t>
+          <t>Bottentömmande behållare (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -14423,17 +15251,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -14443,12 +15271,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -14456,12 +15284,12 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.5</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kärl 370 l restavfall 60 kg</t>
+          <t>Lastväxlarflak (restavfall)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -14471,17 +15299,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -14491,12 +15319,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -14504,12 +15332,12 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.4.2</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kärl 660 l restavfall 100 kg</t>
+          <t>Kärl 240 l (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -14552,12 +15380,12 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Överfullt kärl</t>
+          <t>Kärl 370 l (restavfall)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -14572,12 +15400,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -14592,7 +15420,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14600,12 +15428,12 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.4.3</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Överfull bottentömmande behållare</t>
+          <t>Kärl 660 l (restavfall)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14620,12 +15448,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -14640,7 +15468,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14648,12 +15476,12 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.4.4</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Byte av trasigt kärl vid oaktsamhet</t>
+          <t>Kärl 140 l (matavfall)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -14668,12 +15496,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -14688,7 +15516,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -14696,12 +15524,12 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.4.5</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Byte/återtag av kärl en (1) ggr/år 140–240 liter</t>
+          <t>Bottentömmande behållare (mat-/restavfall)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -14711,17 +15539,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -14731,12 +15559,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -14744,12 +15572,12 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.4.5</t>
+          <t>2.2.6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Byte/återtag av kärl en (1) ggr/år 370–660 liter</t>
+          <t>Lastväxlarflak (restavfall)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -14759,17 +15587,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -14779,12 +15607,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -14792,12 +15620,12 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.4.5</t>
+          <t>2.2.7</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ytterligare byte av kärl under kalenderåret</t>
+          <t>Kärl 140 l (kontors-/returpapper)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -14840,12 +15668,12 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.4.6</t>
+          <t>2.2.7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kärl</t>
+          <t>Egen överlämning av förbrukat kontors-/returpapper enligt anvisning</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -14855,17 +15683,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -14875,12 +15703,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -14888,12 +15716,12 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.4.6</t>
+          <t>2.2.7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bottentömmande behållare</t>
+          <t>Egen överlämning av förbrukat matfett enligt anvisning</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -14936,12 +15764,12 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.4.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kärl 140-660 L 1,5-10</t>
+          <t>Viktavgift matavfall</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -14951,17 +15779,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -14971,12 +15799,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -14984,12 +15812,12 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.4.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kärl 140-660 L 10-20</t>
+          <t>Viktavgift restavfall</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -14999,17 +15827,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -15019,12 +15847,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -15032,12 +15860,12 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.4.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kärl 140-660 L 20-30</t>
+          <t>Lyftavgift kärl</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -15080,12 +15908,12 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.4.7</t>
+          <t>2.4.1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avfallsport/dörr</t>
+          <t>Fakturavgift</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -15128,12 +15956,12 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.4.7</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Låst dörr, med kod</t>
+          <t>Delat kärl 240 l matavfall 40 kg</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -15143,17 +15971,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -15163,12 +15991,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15176,12 +16004,12 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.4.8</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kärl 140 l matavfall</t>
+          <t>Delat kärl 240 l restavfall 40 kg</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -15191,17 +16019,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -15211,12 +16039,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15224,12 +16052,12 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.4.8</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kärl 190 l restavfall</t>
+          <t>Extra kärl 140 l matavfall 60 kg</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -15272,12 +16100,12 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.4.8</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kärl 370 l restavfall</t>
+          <t>Extra kärl 140-190 l restavfall 60 kg</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -15287,17 +16115,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -15307,12 +16135,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15320,12 +16148,12 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.4.8</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kärl 660 l restavfall</t>
+          <t>Kärl 370 l restavfall 60 kg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15340,12 +16168,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -15360,7 +16188,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -15368,12 +16196,12 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.4.8</t>
+          <t>2.4.2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bottentömmande behållare</t>
+          <t>Kärl 660 l restavfall 100 kg</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15383,17 +16211,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -15403,12 +16231,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -15416,12 +16244,12 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.4.9</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sidlastande fordon</t>
+          <t>Överfullt kärl</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15464,12 +16292,12 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.4.9</t>
+          <t>2.4.3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bottentömmande fordon</t>
+          <t>Överfull bottentömmande behållare</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15512,12 +16340,12 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.4.9</t>
+          <t>2.4.4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tömningsavgift per behållare</t>
+          <t>Byte av trasigt kärl vid oaktsamhet</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15527,17 +16355,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -15547,12 +16375,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -15560,12 +16388,12 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.4.10</t>
+          <t>2.4.5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Betalsäck</t>
+          <t>Byte/återtag av kärl en (1) ggr/år 140–240 liter</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -15575,17 +16403,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -15595,12 +16423,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15608,12 +16436,12 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.4.10</t>
+          <t>2.4.5</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Akutsäck</t>
+          <t>Byte/återtag av kärl en (1) ggr/år 370–660 liter</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -15656,12 +16484,12 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.4.11</t>
+          <t>2.4.5</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Matavfallspåsar 9 L</t>
+          <t>Ytterligare byte av kärl under kalenderåret</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -15671,17 +16499,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15691,12 +16519,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -15704,12 +16532,12 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.4.11</t>
+          <t>2.4.6</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Matavfallspåsar 22 L</t>
+          <t>Kärl</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -15752,12 +16580,12 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.4.11</t>
+          <t>2.4.6</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gravitationslås till kärl</t>
+          <t>Bottentömmande behållare</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -15800,12 +16628,12 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.4.11</t>
+          <t>2.4.7</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Extra nyckel till gravitationslås</t>
+          <t>Kärl 140-660 L 1,5-10</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -15815,17 +16643,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15835,12 +16663,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15848,12 +16676,12 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.4.7</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kommunalt avfall</t>
+          <t>Kärl 140-660 L 10-20</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -15863,17 +16691,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15883,12 +16711,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15896,12 +16724,12 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.4.7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Farligt avfall (ej uppmärkt)</t>
+          <t>Kärl 140-660 L 20-30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -15911,17 +16739,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15931,12 +16759,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15944,12 +16772,12 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.4.7</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Farligt avfall (uppmärkt)</t>
+          <t>Avfallsport/dörr</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -15959,17 +16787,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15979,12 +16807,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -15992,12 +16820,12 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>2.4.7</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avisering av ankomst</t>
+          <t>Låst dörr, med kod</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -16007,17 +16835,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16027,12 +16855,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -16040,12 +16868,12 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Upp till 3 m3</t>
+          <t>Kärl 140 l matavfall</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -16055,17 +16883,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16075,12 +16903,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -16088,12 +16916,12 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mellan 3 m3 och 6 m3</t>
+          <t>Kärl 190 l restavfall</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -16108,12 +16936,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Standardtaxa används endast som förslag</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -16128,7 +16956,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Standardtaxa får inte skriva över befintlig kommun-EDP.</t>
         </is>
       </c>
     </row>
@@ -16136,12 +16964,12 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mellan 6 m3 och 9 m3</t>
+          <t>Kärl 370 l restavfall</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -16184,12 +17012,12 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tillägg per m3 över 9 m3</t>
+          <t>Kärl 660 l restavfall</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -16232,12 +17060,12 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.8</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bad-, disk- och tvättbrunn upp till 3 m3</t>
+          <t>Bottentömmande behållare</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -16247,17 +17075,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16267,12 +17095,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -16280,12 +17108,12 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.4.9</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tillägg per m3 över 3 m3</t>
+          <t>Sidlastande fordon</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -16295,17 +17123,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16315,12 +17143,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -16328,12 +17156,12 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.9</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 5-25 m</t>
+          <t>Bottentömmande fordon</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -16343,17 +17171,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16363,12 +17191,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -16376,12 +17204,12 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.9</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 25-35 m</t>
+          <t>Tömningsavgift per behållare</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16391,17 +17219,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16411,12 +17239,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -16424,12 +17252,12 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 36-45 m</t>
+          <t>Betalsäck</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16472,12 +17300,12 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.10</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 46-55 m</t>
+          <t>Akutsäck</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16520,12 +17348,12 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.11</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hantering av brunnslock som väger 15-25 kg</t>
+          <t>Matavfallspåsar 9 L</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16535,17 +17363,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16555,12 +17383,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -16568,12 +17396,12 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Krav på information om tömningstid</t>
+          <t>Matavfallspåsar 22 L</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16616,12 +17444,12 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Krav på närvaro vid specificerad tömningstid</t>
+          <t>Gravitationslås till kärl</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16664,12 +17492,12 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.4.11</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hantering av kod för kodlås vid slamtömning</t>
+          <t>Extra nyckel till gravitationslås</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -16712,12 +17540,12 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hetvattentvätt med spolbil, timersättning</t>
+          <t>Kommunalt avfall</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -16760,12 +17588,12 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tömning av extra tank/brunn i samband med ordinarie/budad tömning upp till 5 m3</t>
+          <t>Farligt avfall (ej uppmärkt)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -16808,12 +17636,12 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
+          <t>Farligt avfall (uppmärkt)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -16856,12 +17684,12 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Budning utanför ordinarie tömningsperiod (1 nov – 30 april)</t>
+          <t>Avisering av ankomst</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -16904,12 +17732,12 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tömning av toalettvagnar eller liknande /styck</t>
+          <t>Upp till 3 m3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -16952,12 +17780,12 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Latrinbehållare 37 liter inkl. mottagning och behandling</t>
+          <t>Mellan 3 m3 och 6 m3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -17000,12 +17828,12 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Filtermassor upp till 500 kg</t>
+          <t>Mellan 6 m3 och 9 m3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -17048,12 +17876,12 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Filtermassor 500-1000 kg</t>
+          <t>Tillägg per m3 över 9 m3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -17063,17 +17891,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -17083,12 +17911,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -17096,12 +17924,12 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Krav på information om hämtningstid</t>
+          <t>Bad-, disk- och tvättbrunn upp till 3 m3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -17144,12 +17972,12 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Krav på närvaro vid specificerad hämtningstid</t>
+          <t>Tillägg per m3 över 3 m3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -17159,17 +17987,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17179,12 +18007,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -17192,12 +18020,12 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hantering av kod för kodlås</t>
+          <t>Dragning av extra slang vid 5-25 m</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -17207,17 +18035,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -17227,12 +18055,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -17240,12 +18068,12 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Upp till 3 m3</t>
+          <t>Dragning av extra slang vid 25-35 m</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -17288,12 +18116,12 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mellan 3 m3 och 6 m3</t>
+          <t>Dragning av extra slang vid 36-45 m</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -17303,17 +18131,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17323,12 +18151,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -17336,12 +18164,12 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Över 6 m3</t>
+          <t>Dragning av extra slang vid 46-55 m</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -17384,12 +18212,12 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 5-25 m</t>
+          <t>Hantering av brunnslock som väger 15-25 kg</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17432,12 +18260,12 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 25-35 m</t>
+          <t>Krav på information om tömningstid</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17480,12 +18308,12 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 36-45 m</t>
+          <t>Krav på närvaro vid specificerad tömningstid</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17528,12 +18356,12 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dragning av extra slang vid 46-55 m</t>
+          <t>Hantering av kod för kodlås vid slamtömning</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17543,17 +18371,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -17563,12 +18391,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -17576,12 +18404,12 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hantering av brunnslock som väger 15-25 kg</t>
+          <t>Hetvattentvätt med spolbil, timersättning</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17624,12 +18452,12 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Krav på information om tömningstid</t>
+          <t>Tömning av extra tank/brunn i samband med ordinarie/budad tömning upp till 5 m3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17672,12 +18500,12 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Krav på närvaro vid specificerad tömningstid</t>
+          <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17687,17 +18515,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -17707,12 +18535,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -17720,12 +18548,12 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Hantering av kod för kodlås vid tömning</t>
+          <t>Budning utanför ordinarie tömningsperiod (1 nov – 30 april)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -17735,17 +18563,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -17755,12 +18583,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -17768,12 +18596,12 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hetvattentvätt med spolbil, timersättning</t>
+          <t>Tömning av toalettvagnar eller liknande /styck</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -17783,17 +18611,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -17803,12 +18631,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -17816,12 +18644,12 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Silikontätning per lock</t>
+          <t>Latrinbehållare 37 liter inkl. mottagning och behandling</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -17864,12 +18692,12 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tömning av extra tank i samband med ordinarie/budad tömning upp till 5 m3</t>
+          <t>Filtermassor upp till 500 kg</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -17912,12 +18740,12 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
+          <t>Filtermassor 500-1000 kg</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17960,12 +18788,12 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Budning utanför ordinarie tömningsperiod</t>
+          <t>Krav på information om hämtningstid</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17975,17 +18803,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -17995,12 +18823,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18008,12 +18836,12 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Verksamheter</t>
+          <t>Krav på närvaro vid specificerad hämtningstid</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18056,12 +18884,12 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Övriga abonnemangstyper</t>
+          <t>Hantering av kod för kodlås</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18104,12 +18932,12 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Vågkort</t>
+          <t>Upp till 3 m3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -18152,12 +18980,12 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Borttappat vågkort</t>
+          <t>Mellan 3 m3 och 6 m3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -18167,17 +18995,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -18187,12 +19015,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -18200,12 +19028,12 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ej redovisad ankomst till ÅVC (för företagare och privatpersoner som lämnar verksamhetsavfall utan att anmäla sin ankomst)</t>
+          <t>Över 6 m3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -18248,12 +19076,12 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6.1.1</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ej redovisad eller fel redovisad fraktion av avfall</t>
+          <t>Dragning av extra slang vid 5-25 m</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -18263,17 +19091,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -18283,12 +19111,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18296,12 +19124,12 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avfall till energiåtervinning (240 L sopsäck)</t>
+          <t>Dragning av extra slang vid 25-35 m</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18311,17 +19139,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -18331,12 +19159,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18344,12 +19172,12 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avfall till energiåtervinning</t>
+          <t>Dragning av extra slang vid 36-45 m</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18359,17 +19187,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -18379,12 +19207,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18392,12 +19220,12 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Skrymmande avfall till energiåtervinning större än 20×20×80</t>
+          <t>Dragning av extra slang vid 46-55 m</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18440,12 +19268,12 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Träavfall – obehandlat, utan tapet, plastmatta, tjärpapp</t>
+          <t>Hantering av brunnslock som väger 15-25 kg</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18488,12 +19316,12 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Träavfall – behandlat, utan tapet, plastmatta, tjärpapp</t>
+          <t>Krav på information om tömningstid</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18536,12 +19364,12 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tryckimpregnerat virke, pall</t>
+          <t>Krav på närvaro vid specificerad tömningstid</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18584,12 +19412,12 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Betong, lättbetong</t>
+          <t>Hantering av kod för kodlås vid tömning</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18599,17 +19427,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -18619,12 +19447,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18632,12 +19460,12 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Gips, gipsskivor</t>
+          <t>Hetvattentvätt med spolbil, timersättning</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18647,17 +19475,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -18667,12 +19495,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18680,12 +19508,12 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tegel</t>
+          <t>Silikontätning per lock</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -18728,12 +19556,12 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fönster- och planglas utan karm</t>
+          <t>Tömning av extra tank i samband med ordinarie/budad tömning upp till 5 m3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -18743,17 +19571,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -18763,12 +19591,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18776,12 +19604,12 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Fönster med karm</t>
+          <t>Budning inom ordinarie tömningsperiod (1 maj- 31 oktober)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -18791,17 +19619,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Rad finns men saknar Taxakod</t>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -18811,12 +19639,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Taxa finns som rad. EDP-koppling saknas.</t>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>
       </c>
     </row>
@@ -18824,12 +19652,12 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Plast</t>
+          <t>Budning utanför ordinarie tömningsperiod</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18872,12 +19700,12 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Isolering utan innehåll av asbest</t>
+          <t>Verksamheter</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18920,12 +19748,12 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Klinker, keramik, porslin</t>
+          <t>Övriga abonnemangstyper</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18935,17 +19763,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -18955,12 +19783,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -18968,12 +19796,12 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Handfat</t>
+          <t>Vågkort</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18983,17 +19811,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -19003,12 +19831,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19016,12 +19844,12 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>WC-stol</t>
+          <t>Borttappat vågkort</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19031,17 +19859,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -19051,12 +19879,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19064,12 +19892,12 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Metall</t>
+          <t>Ej redovisad ankomst till ÅVC (för företagare och privatpersoner som lämnar verksamhetsavfall utan att anmäla sin ankomst)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -19112,12 +19940,12 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6.1.2</t>
+          <t>6.1.1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Textilier</t>
+          <t>Ej redovisad eller fel redovisad fraktion av avfall</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -19165,7 +19993,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Fiskeredskap</t>
+          <t>Avfall till energiåtervinning (240 L sopsäck)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -19213,7 +20041,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ätbart fett/frityrolja</t>
+          <t>Avfall till energiåtervinning</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -19261,7 +20089,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kvistar och grenar</t>
+          <t>Skrymmande avfall till energiåtervinning större än 20×20×80</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19309,7 +20137,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jord</t>
+          <t>Träavfall – obehandlat, utan tapet, plastmatta, tjärpapp</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19319,17 +20147,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -19339,12 +20167,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19357,7 +20185,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sten</t>
+          <t>Träavfall – behandlat, utan tapet, plastmatta, tjärpapp</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19367,17 +20195,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -19387,12 +20215,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19405,7 +20233,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Stubbar/rötter för krossning</t>
+          <t>Tryckimpregnerat virke, pall</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19453,7 +20281,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Flera fraktioner för egen sortering på ramp (max 2 m³)</t>
+          <t>Betong, lättbetong</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19501,7 +20329,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Osorterat avfall till sortering (ej innehåll av farligt avfall och elavfall)</t>
+          <t>Gips, gipsskivor</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19549,7 +20377,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tonerkassetter, utan elektronik/chip</t>
+          <t>Tegel</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19559,17 +20387,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -19579,12 +20407,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19597,7 +20425,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Oljeemulsion, emballerat</t>
+          <t>Fönster- och planglas utan karm</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19645,7 +20473,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Förorenad olja innehållande PCB</t>
+          <t>Fönster med karm</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -19655,17 +20483,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -19675,12 +20503,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19693,7 +20521,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Oljeavskiljarslam</t>
+          <t>Plast</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -19741,7 +20569,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Isolering utan innehåll av asbest</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -19751,17 +20579,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Word-taxa saknar EDP-match och standardförslag</t>
+          <t>Rad finns men saknar Taxakod</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -19771,12 +20599,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+          <t>Taxa finns som rad. EDP-koppling saknas.</t>
         </is>
       </c>
     </row>
@@ -19789,7 +20617,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bensinrester</t>
+          <t>Klinker, keramik, porslin</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -19837,7 +20665,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hydralslang, med/utan koppling</t>
+          <t>Handfat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -19885,7 +20713,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Förpackningar, tömde ej rengjorda</t>
+          <t>WC-stol</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -19933,7 +20761,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Oljeavfall, fast osorterat emba</t>
+          <t>Metall</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -19981,7 +20809,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Absorbermedel, filtermaterial</t>
+          <t>Textilier</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20029,7 +20857,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Oljefilter</t>
+          <t>Fiskeredskap</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20077,7 +20905,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bromsvätska</t>
+          <t>Ätbart fett/frityrolja</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -20125,7 +20953,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Transformator, kondensator med PCB</t>
+          <t>Kvistar och grenar</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -20173,7 +21001,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Fogskum</t>
+          <t>Jord</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -20221,7 +21049,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Halon</t>
+          <t>Sten</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -20269,7 +21097,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Koldioxid</t>
+          <t>Stubbar/rötter för krossning</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -20317,7 +21145,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Brandsläckare</t>
+          <t>Flera fraktioner för egen sortering på ramp (max 2 m³)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -20365,7 +21193,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Helium</t>
+          <t>Osorterat avfall till sortering (ej innehåll av farligt avfall och elavfall)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -20413,7 +21241,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tändare</t>
+          <t>Tonerkassetter, utan elektronik/chip</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -20461,7 +21289,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Syrgas</t>
+          <t>Oljeemulsion, emballerat</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -20509,7 +21337,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Oxiderande fast ämne/vätska</t>
+          <t>Förorenad olja innehållande PCB</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -20557,7 +21385,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Klorex</t>
+          <t>Oljeavskiljarslam</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -20605,7 +21433,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Aerosoler isocyanat, bekämpning</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -20653,7 +21481,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Gasol inkl tub</t>
+          <t>Bensinrester</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -20701,7 +21529,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Gasol, blå programmet</t>
+          <t>Hydralslang, med/utan koppling</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -20749,7 +21577,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Giftig organisk vätska</t>
+          <t>Förpackningar, tömde ej rengjorda</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -20797,7 +21625,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Småkemikalier, ej Hg-haltiga</t>
+          <t>Oljeavfall, fast osorterat emba</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -20845,7 +21673,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Giftig oorganisk vätska</t>
+          <t>Absorbermedel, filtermaterial</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -20893,7 +21721,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Oxidationsmedel, flytande</t>
+          <t>Oljefilter</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -20941,7 +21769,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Asbest, emballerat</t>
+          <t>Bromsvätska</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -20989,7 +21817,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Smittförande avfall</t>
+          <t>Transformator, kondensator med PCB</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -21037,7 +21865,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Lösningsmedel</t>
+          <t>Fogskum</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -21085,7 +21913,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Väteperoxid</t>
+          <t>Halon</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -21133,7 +21961,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Flourvätesyra</t>
+          <t>Koldioxid</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -21181,7 +22009,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Svavelsyra</t>
+          <t>Brandsläckare</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21229,7 +22057,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Salpetersyra</t>
+          <t>Helium</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -21277,7 +22105,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Surt oorganisk fast ämne</t>
+          <t>Tändare</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -21325,7 +22153,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Surt organisk fast ämne</t>
+          <t>Syrgas</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -21373,7 +22201,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Surt oorganisk vätska</t>
+          <t>Oxiderande fast ämne/vätska</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -21421,7 +22249,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Surt organisk vätska</t>
+          <t>Klorex</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -21469,7 +22297,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ammoniaklösning</t>
+          <t>Aerosoler isocyanat, bekämpning</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -21517,7 +22345,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Alkaliskt avfall fast</t>
+          <t>Gasol inkl tub</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -21565,7 +22393,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Basiskt organiskt fast/flytande</t>
+          <t>Gasol, blå programmet</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -21613,7 +22441,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Fotokemikalier</t>
+          <t>Giftig organisk vätska</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -21661,7 +22489,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bekämpningsmedel aerosoler</t>
+          <t>Småkemikalier, ej Hg-haltiga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -21709,7 +22537,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bekämpningsmedel fast</t>
+          <t>Giftig oorganisk vätska</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -21757,7 +22585,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bekämpningsmedel flytande</t>
+          <t>Oxidationsmedel, flytande</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -21805,7 +22633,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Kvicksilverhaltigt avfall</t>
+          <t>Asbest, emballerat</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -21853,7 +22681,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kvicksilver i föremål</t>
+          <t>Smittförande avfall</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -21901,7 +22729,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Oljehaltigt avfall (ej PCB)</t>
+          <t>Lösningsmedel</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -21949,7 +22777,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Olja förorenad (ej PCB)</t>
+          <t>Väteperoxid</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -21997,7 +22825,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Färg-, lack-, limburkar lösning</t>
+          <t>Flourvätesyra</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -22045,7 +22873,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Färg-, lack-, limburkar lösning aerosoler</t>
+          <t>Svavelsyra</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -22093,7 +22921,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Isocyanater</t>
+          <t>Salpetersyra</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -22141,7 +22969,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Härdare metyl- etylketonperoxid</t>
+          <t>Surt oorganisk fast ämne</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -22189,7 +23017,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Härdare dibenzoylperoxid</t>
+          <t>Surt organisk fast ämne</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -22237,7 +23065,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Färg-,lack-, limburkar vattenbaserade</t>
+          <t>Surt oorganisk vätska</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -22285,7 +23113,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tensida alkaliska flytande avfall</t>
+          <t>Surt organisk vätska</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -22333,7 +23161,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Rengöring/vaskmedel fast</t>
+          <t>Ammoniaklösning</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -22381,7 +23209,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Alkaliska flytande avfall</t>
+          <t>Alkaliskt avfall fast</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -22429,7 +23257,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Cytotoxiska läkemedel, cytostat</t>
+          <t>Basiskt organiskt fast/flytande</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -22477,7 +23305,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Rökdetektor med andra isotoper</t>
+          <t>Fotokemikalier</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -22525,7 +23353,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Rökdetektor med Am 241</t>
+          <t>Bekämpningsmedel aerosoler</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -22573,7 +23401,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Batterier stav, pencell</t>
+          <t>Bekämpningsmedel fast</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -22621,7 +23449,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Batterier lithium</t>
+          <t>Bekämpningsmedel flytande</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -22669,7 +23497,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bil-, mcbatteri med bly</t>
+          <t>Kvicksilverhaltigt avfall</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -22717,7 +23545,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Glödlampor</t>
+          <t>Kvicksilver i föremål</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -22765,7 +23593,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lysrör</t>
+          <t>Oljehaltigt avfall (ej PCB)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -22813,7 +23641,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Elavfall, små elektronik</t>
+          <t>Olja förorenad (ej PCB)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -22861,7 +23689,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>El-avfall fast installation</t>
+          <t>Färg-, lack-, limburkar lösning</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -22909,7 +23737,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>El-avfall kabel</t>
+          <t>Färg-, lack-, limburkar lösning aerosoler</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -22957,7 +23785,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Toner, färgpatron med elektronik</t>
+          <t>Isocyanater</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -23005,7 +23833,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Tv, radio, skärm, skrivare utan färgpatron</t>
+          <t>Härdare metyl- etylketonperoxid</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -23053,7 +23881,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Kyl-, frysskåp, -box</t>
+          <t>Härdare dibenzoylperoxid</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -23101,7 +23929,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Kyl-, frysskåp, -box från verksamhet</t>
+          <t>Färg-,lack-, limburkar vattenbaserade</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -23149,7 +23977,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spis, tvätt-, diskmaskin</t>
+          <t>Tensida alkaliska flytande avfall</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -23197,7 +24025,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spis, tvätt-, diskmaskin från verksamhet</t>
+          <t>Rengöring/vaskmedel fast</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -23240,12 +24068,12 @@
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Container X m3</t>
+          <t>Alkaliska flytande avfall</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -23288,12 +24116,12 @@
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Container X m3</t>
+          <t>Cytotoxiska läkemedel, cytostat</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -23336,12 +24164,12 @@
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Container X m3</t>
+          <t>Rökdetektor med andra isotoper</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -23384,12 +24212,12 @@
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Omklassning av felsorterad container</t>
+          <t>Rökdetektor med Am 241</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -23432,12 +24260,12 @@
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="inlineStr">
         <is>
-          <t>6.1.4</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Okänt farligt avfall (säkerhetsdatablad saknas)</t>
+          <t>Batterier stav, pencell</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -23480,12 +24308,12 @@
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="inlineStr">
         <is>
-          <t>6.1.4</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ombud för rapportering av farligt avfall i Avfallsregistret</t>
+          <t>Batterier lithium</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -23528,12 +24356,12 @@
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="inlineStr">
         <is>
-          <t>6.1.4</t>
+          <t>6.1.2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Administrativ rapporteringsavgift till Avfallsregistret</t>
+          <t>Bil-, mcbatteri med bly</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -23576,45 +24404,909 @@
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr">
         <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Glödlampor</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Lysrör</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Elavfall, små elektronik</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>El-avfall fast installation</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>El-avfall kabel</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Toner, färgpatron med elektronik</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Tv, radio, skärm, skrivare utan färgpatron</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Kyl-, frysskåp, -box</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Kyl-, frysskåp, -box från verksamhet</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Spis, tvätt-, diskmaskin</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>6.1.2</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Spis, tvätt-, diskmaskin från verksamhet</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>6.1.3</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Container X m3</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>6.1.3</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Container X m3</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>6.1.3</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Container X m3</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>6.1.3</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Omklassning av felsorterad container</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
           <t>6.1.4</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Okänt farligt avfall (säkerhetsdatablad saknas)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>6.1.4</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Ombud för rapportering av farligt avfall i Avfallsregistret</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>6.1.4</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Administrativ rapporteringsavgift till Avfallsregistret</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Word-taxa saknar EDP-match och standardförslag</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>TaxDecisionEngine</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>6.1.4</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
         <is>
           <t>Ombud för registrering av El-kretsen avlämnarintyg i Hämtplatsportalen</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>Beslut</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>NEW_TAXA</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
         <is>
           <t>Word</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
+      <c r="G265" t="inlineStr">
         <is>
           <t>Word-taxa saknar EDP-match och standardförslag</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
+      <c r="H265" t="inlineStr">
         <is>
           <t>TaxDecisionEngine</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>NEW_TAXA</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>NEW_TAXA</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
         <is>
           <t>Skapa/hantera som ny taxa eller manuell granskning.</t>
         </is>

--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
+          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym. Skillnader property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
+          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym. Skillnader property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Extra. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='190', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Byte. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.58 justerad=0.63. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='Abonnemang' kandidat='Extra'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Abonnemang, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2105,17 +2105,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2335,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2377,17 +2377,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Matavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.60 justerad=0.65. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='140' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Matavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='140', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RM26FRI score=0.54 justerad=0.64. Matchar waste_type: Matavfall, container_type: Kärl, container_volume_liter: 240. Skillnader category: Word='Hushåll' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', property_type: Word='' kandidat='Fritidshus', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240. Skillnader waste_type: Word='Matavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Matavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 140. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Matavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 140. Skillnader property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190. Skillnader property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -3052,17 +3052,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3287,17 +3287,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3423,17 +3423,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3470,17 +3470,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3512,17 +3512,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Extra'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Extra', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -3784,17 +3784,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.29 justerad=0.34. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning. Skillnader container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.29 justerad=0.34. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning. Skillnader container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4036,17 +4036,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Hushåll, service_type: Abonnemang, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.46 justerad=0.51. Matchar category: Hushåll, service_type: Hämtning/tömning, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4078,17 +4078,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Hushåll, service_type: Abonnemang, container_volume_liter: 22, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.42 justerad=0.47. Matchar category: Hushåll, service_type: Hämtning/tömning, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='22' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Matavfall, service_type: Hämtning/tömning, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='140', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Extra. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='190', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4251,17 +4251,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Hushåll, waste_type: Farligt avfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4293,17 +4293,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Hushåll, waste_type: Farligt avfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Flerbostad/verksamhet, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 9m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 9m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.55 justerad=0.59. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.30 justerad=0.35. Matchar category: Flerbostad/verksamhet, container_type: Brunn. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='Vikt' kandidat='Volym', factor_hint: Word='VIKG' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.26 justerad=0.31. Matchar category: Flerbostad/verksamhet. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.33 justerad=0.38. Matchar category: Flerbostad/verksamhet, unit_type: Styck, factor_hint: ST. Skillnader service_type: Word='Hämtning/tömning' kandidat='Abonnemang', container_type: Word='' kandidat='Latrin', container_volume_liter: Word='' kandidat='37'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Styck' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Flerbostad/verksamhet, service_type: Abonnemang, container_type: Latrin, container_volume_liter: 37. Skillnader unit_type: Word='Behållarvolym' kandidat='Styck', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ST'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Flerbostad/verksamhet, service_type: Abonnemang, container_type: Latrin, container_volume_liter: 37. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Behållarvolym' kandidat='Styck', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ST'</t>
         </is>
       </c>
     </row>
@@ -5272,17 +5272,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.20 justerad=0.26. Matchar unit_type: Vikt, factor_hint: VIKG. Skillnader category: Word='Tilläggstjänst' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Mottagning/behandling' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5319,17 +5319,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.20 justerad=0.26. Matchar unit_type: Vikt, factor_hint: VIKG. Skillnader category: Word='Tilläggstjänst' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Mottagning/behandling' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5361,17 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.27 justerad=0.32. Matchar category: Tilläggstjänst, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5403,17 +5403,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.27 justerad=0.32. Matchar category: Tilläggstjänst, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5492,17 +5492,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='3m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5539,17 +5539,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='3m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5586,17 +5586,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='6m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -5628,17 +5628,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5670,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -5712,17 +5712,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -5754,17 +5754,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.33 justerad=0.33. Matchar category: Slam, container_type: Brunn. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.48 justerad=0.48. Matchar category: Slam, waste_type: Slam, container_type: Brunn. Skillnader service_type: Word='Extra' kandidat='Abonnemang', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.27 justerad=0.27. Matchar category: Slam. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.27 justerad=0.27. Matchar category: Slam. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Slam, service_type: Extra, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Slam, service_type: Extra, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Slam' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -6189,17 +6189,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.23 justerad=0.28. Matchar category: Verksamhetsavfall. Skillnader container_type: Word='' kandidat='Container', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Volym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.27 justerad=0.37. Matchar service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.32 justerad=0.32. Matchar service_type: Abonnemang, property_type: Verksamhet. Skillnader category: Word='Verksamhetsavfall' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD FPASÄCK240 score=0.42 justerad=0.42. Matchar category: ÅVC/verksamhetsavfall, container_type: Säck, container_volume_liter: 240. Skillnader service_type: Word='' kandidat='Abonnemang', unit_type: Word='Styck' kandidat='Behållarvolym', factor_hint: Word='ST' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FPASÄCK240 score=0.50 justerad=0.50. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, container_volume_liter: 240. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym', factor_hint: Word='ST' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -6493,17 +6493,17 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tryckimpregnerat trä, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tryckimpregnerat trä, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Betong, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Betong, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tegel, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Gips' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -6908,17 +6908,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP TEST370VV score=0.29 justerad=0.39. Matchar waste_type: Plast. Skillnader category: Word='ÅVC/verksamhetsavfall' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', unit_type: Word='Vikt' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest. Skillnader unit_type: Word='Volym' kandidat='Vikt', factor_hint: Word='VOLM' kandidat='VIKG'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7118,17 +7118,17 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP Miljövagn score=0.27 justerad=0.36. Matchar waste_type: Metall. Skillnader category: Word='ÅVC/verksamhetsavfall' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7244,17 +7244,17 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Oljeavfall', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.34 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.34 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Vikt', factor_hint: Word='' kandidat='VIKG'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Vikt', factor_hint: Word='' kandidat='VIKG'</t>
         </is>
       </c>
     </row>
@@ -7523,17 +7523,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Farligt avfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7711,17 +7711,17 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7758,17 +7758,17 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7805,17 +7805,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -8087,17 +8087,17 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8134,17 +8134,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8181,17 +8181,17 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8228,17 +8228,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8275,17 +8275,17 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8322,17 +8322,17 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8369,17 +8369,17 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8416,17 +8416,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8463,17 +8463,17 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8510,17 +8510,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8557,17 +8557,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8604,17 +8604,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8651,17 +8651,17 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8698,17 +8698,17 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8745,17 +8745,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8839,17 +8839,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9826,17 +9826,17 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.56 justerad=0.61. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -9873,17 +9873,17 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.56 justerad=0.61. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -9977,7 +9977,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.28 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='Batterier' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.28 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='Batterier' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10823,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10917,7 +10917,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -10954,17 +10954,17 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: ÅVC/verksamhetsavfall, waste_type: Kyl/frys. Skillnader unit_type: Word='Styck' kandidat='Vikt', factor_hint: Word='ST' kandidat='VIKG'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Kyl/frys, unit_type: Vikt, factor_hint: VIKG. Skillnader property_type: Word='Verksamhet' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang', property_type: Word='Verksamhet' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Verksamhetsavfall, container_type: Container. Skillnader container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Verksamhetsavfall, container_type: Container. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP EJKLASSFA score=0.37 justerad=0.47. Matchar waste_type: Farligt avfall, service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP EJKLASSFA score=0.37 justerad=0.47. Matchar waste_type: Farligt avfall, service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Tillfälle'</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar waste_type: Farligt avfall, service_type: Abonnemang, unit_type: Tillfälle, factor_hint: TILLFÄLLE. Skillnader category: Word='Verksamhetsavfall' kandidat='Hushåll'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar waste_type: Farligt avfall, service_type: Abonnemang, unit_type: Tillfälle, factor_hint: TILLFÄLLE. Skillnader category: Word='Verksamhetsavfall' kandidat='Hushåll', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11424,17 +11424,17 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.26 justerad=0.31. Matchar category: Verksamhetsavfall, unit_type: Tillfälle, factor_hint: TILLFÄLLE</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.24 justerad=0.34. Matchar service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25547,7 +25547,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
+          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym. Skillnader property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25643,7 +25643,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
+          <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym. Skillnader property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -25739,7 +25739,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Extra. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='190', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -25787,7 +25787,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Byte. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -25979,7 +25979,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26027,7 +26027,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26075,7 +26075,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26219,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26242,17 +26242,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -26262,12 +26262,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.58 justerad=0.63. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='Abonnemang' kandidat='Extra'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26315,7 +26315,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Abonnemang, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26338,17 +26338,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -26358,12 +26358,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -26411,7 +26411,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26459,7 +26459,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26507,7 +26507,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26555,7 +26555,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26578,17 +26578,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -26598,12 +26598,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -26626,17 +26626,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -26646,12 +26646,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26747,7 +26747,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26795,7 +26795,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26843,7 +26843,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -26866,17 +26866,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -26886,12 +26886,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -26914,17 +26914,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -26934,12 +26934,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -26987,7 +26987,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Matavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.60 justerad=0.65. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='140' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -27035,7 +27035,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27083,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Matavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='140', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27179,7 +27179,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27227,7 +27227,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27275,7 +27275,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27298,17 +27298,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -27318,12 +27318,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RM26FRI score=0.54 justerad=0.64. Matchar waste_type: Matavfall, container_type: Kärl, container_volume_liter: 240. Skillnader category: Word='Hushåll' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', property_type: Word='' kandidat='Fritidshus', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240. Skillnader waste_type: Word='Matavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27371,7 +27371,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27419,7 +27419,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Matavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 140. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Matavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 140. Skillnader property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190. Skillnader property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27515,7 +27515,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27563,7 +27563,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.64 justerad=0.69. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660. Skillnader service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27634,17 +27634,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -27654,12 +27654,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -27707,7 +27707,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -27851,7 +27851,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27874,17 +27874,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -27894,12 +27894,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27947,7 +27947,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -27970,17 +27970,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -27990,12 +27990,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28018,17 +28018,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -28038,12 +28038,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28066,17 +28066,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -28086,12 +28086,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28114,17 +28114,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -28134,12 +28134,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28162,17 +28162,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -28182,12 +28182,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28283,7 +28283,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Extra'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Extra', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28331,7 +28331,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28379,7 +28379,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28402,17 +28402,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -28422,12 +28422,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28475,7 +28475,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28523,7 +28523,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl. Skillnader service_type: Word='Byte' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28571,7 +28571,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -28619,7 +28619,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.29 justerad=0.34. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning. Skillnader container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28667,7 +28667,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.29 justerad=0.34. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.55 justerad=0.60. Matchar category: Hushåll, waste_type: Restavfall, service_type: Hämtning/tömning. Skillnader container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28690,17 +28690,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -28710,12 +28710,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Hushåll, service_type: Abonnemang, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.46 justerad=0.51. Matchar category: Hushåll, service_type: Hämtning/tömning, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28738,17 +28738,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -28758,12 +28758,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Hushåll, service_type: Abonnemang, container_volume_liter: 22, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.42 justerad=0.47. Matchar category: Hushåll, service_type: Hämtning/tömning, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='Säck' kandidat='Kärl', container_volume_liter: Word='22' kandidat='240', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.65 justerad=0.70. Matchar category: Hushåll, waste_type: Matavfall, service_type: Hämtning/tömning, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='140', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
     </row>
@@ -28859,7 +28859,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.40 justerad=0.45. Matchar category: Hushåll, service_type: Extra. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='190', unit_type: Word='' kandidat='Behållarvolym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28907,7 +28907,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28930,17 +28930,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -28950,12 +28950,12 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Hushåll, waste_type: Farligt avfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -28978,17 +28978,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -28998,12 +28998,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Hushåll, waste_type: Farligt avfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -29051,7 +29051,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Extra, container_type: Kärl. Skillnader waste_type: Word='Farligt avfall' kandidat='Restavfall', container_volume_liter: Word='' kandidat='190', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29147,7 +29147,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29195,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Flerbostad/verksamhet, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29243,7 +29243,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 9m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: Flerbostad/verksamhet, container_volume_liter: 9m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='', container_type: Word='Kärl' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29291,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.55 justerad=0.59. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29339,7 +29339,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.47 justerad=0.52. Matchar category: Flerbostad/verksamhet, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Flerbostad/verksamhet, container_type: Brunn, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Farligt avfall' kandidat='', service_type: Word='Extra' kandidat='Hämtning/tömning', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29387,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29483,7 +29483,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29531,7 +29531,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Extra. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29579,7 +29579,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.30 justerad=0.35. Matchar category: Flerbostad/verksamhet, container_type: Brunn. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='Vikt' kandidat='Volym', factor_hint: Word='VIKG' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='5m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29675,7 +29675,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29723,7 +29723,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.26 justerad=0.31. Matchar category: Flerbostad/verksamhet. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: Flerbostad/verksamhet, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
         </is>
       </c>
     </row>
@@ -29819,7 +29819,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Flerbostad/verksamhet, service_type: Extra, container_type: Brunn, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -29867,7 +29867,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29915,7 +29915,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning. Skillnader container_type: Word='' kandidat='Brunn', container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -29963,7 +29963,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.33 justerad=0.38. Matchar category: Flerbostad/verksamhet, unit_type: Styck, factor_hint: ST. Skillnader service_type: Word='Hämtning/tömning' kandidat='Abonnemang', container_type: Word='' kandidat='Latrin', container_volume_liter: Word='' kandidat='37'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: Flerbostad/verksamhet, service_type: Hämtning/tömning, container_type: Brunn. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Styck' kandidat='Volym'</t>
         </is>
       </c>
     </row>
@@ -30011,7 +30011,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Flerbostad/verksamhet, service_type: Abonnemang, container_type: Latrin, container_volume_liter: 37. Skillnader unit_type: Word='Behållarvolym' kandidat='Styck', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ST'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: Flerbostad/verksamhet, service_type: Abonnemang, container_type: Latrin, container_volume_liter: 37. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Behållarvolym' kandidat='Styck', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ST'</t>
         </is>
       </c>
     </row>
@@ -30034,17 +30034,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -30054,12 +30054,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.20 justerad=0.26. Matchar unit_type: Vikt, factor_hint: VIKG. Skillnader category: Word='Tilläggstjänst' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Mottagning/behandling' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30082,17 +30082,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -30102,12 +30102,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.20 justerad=0.26. Matchar unit_type: Vikt, factor_hint: VIKG. Skillnader category: Word='Tilläggstjänst' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Mottagning/behandling' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30130,17 +30130,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -30150,12 +30150,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.27 justerad=0.32. Matchar category: Tilläggstjänst, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30178,17 +30178,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -30198,12 +30198,12 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.27 justerad=0.32. Matchar category: Tilläggstjänst, service_type: Hämtning/tömning. Skillnader unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='TILLFÄLLE'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30251,7 +30251,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Tilläggstjänst' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30274,17 +30274,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -30294,12 +30294,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='3m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30322,17 +30322,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -30342,12 +30342,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 3m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='3m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30370,17 +30370,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -30390,12 +30390,12 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: Slam, container_volume_liter: 6m3, unit_type: Volym, factor_hint: VOLM. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BDT03SL score=0.48 justerad=0.58. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning. Skillnader container_type: Word='Latrin' kandidat='', container_volume_liter: Word='6m3' kandidat='', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Volym' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30418,17 +30418,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -30438,12 +30438,12 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -30466,17 +30466,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -30486,12 +30486,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -30514,17 +30514,17 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -30534,12 +30534,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -30562,17 +30562,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -30582,12 +30582,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Slam, service_type: Extra. Skillnader container_volume_liter: Word='' kandidat='5m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FASTSL score=0.40 justerad=0.40. Matchar category: Slam, waste_type: Slam. Skillnader service_type: Word='Extra' kandidat='Abonnemang', container_type: Word='Latrin' kandidat='', property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -30635,7 +30635,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.33 justerad=0.33. Matchar category: Slam, container_type: Brunn. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.48 justerad=0.48. Matchar category: Slam, waste_type: Slam, container_type: Brunn. Skillnader service_type: Word='Extra' kandidat='Abonnemang', property_type: Word='Flerbostadshus' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -30779,7 +30779,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.27 justerad=0.27. Matchar category: Slam. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD BRN03SLORD score=0.27 justerad=0.27. Matchar category: Slam. Skillnader waste_type: Word='' kandidat='Slam', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='ÅRKV'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -30923,7 +30923,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Slam, service_type: Extra, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: Slam, service_type: Extra, container_volume_liter: 5m3, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Slam' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Flerbostadshus' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -30971,7 +30971,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.34 justerad=0.44. Matchar category: Slam, service_type: Hämtning/tömning. Skillnader waste_type: Word='' kandidat='Slam', container_type: Word='' kandidat='Brunn', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BRN03SL score=0.59 justerad=0.69. Matchar category: Slam, waste_type: Slam, service_type: Hämtning/tömning, container_type: Brunn. Skillnader property_type: Word='Flerbostadshus' kandidat='', factor_hint: Word='' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -31042,17 +31042,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -31062,12 +31062,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.23 justerad=0.28. Matchar category: Verksamhetsavfall. Skillnader container_type: Word='' kandidat='Container', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Volym'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Hämtning/tömning' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31115,7 +31115,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.27 justerad=0.37. Matchar service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31163,7 +31163,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31211,7 +31211,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31259,7 +31259,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.32 justerad=0.32. Matchar service_type: Abonnemang, property_type: Verksamhet. Skillnader category: Word='Verksamhetsavfall' kandidat='ÅVC/verksamhetsavfall', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31307,7 +31307,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.20 justerad=0.29. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.26 justerad=0.35. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Brunn' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31355,7 +31355,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD FPASÄCK240 score=0.42 justerad=0.42. Matchar category: ÅVC/verksamhetsavfall, container_type: Säck, container_volume_liter: 240. Skillnader service_type: Word='' kandidat='Abonnemang', unit_type: Word='Styck' kandidat='Behållarvolym', factor_hint: Word='ST' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD FPASÄCK240 score=0.50 justerad=0.50. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, container_volume_liter: 240. Skillnader waste_type: Word='Träavfall' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym', factor_hint: Word='ST' kandidat='KVAN'</t>
         </is>
       </c>
     </row>
@@ -31378,17 +31378,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -31398,12 +31398,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -31426,17 +31426,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -31446,12 +31446,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -31499,7 +31499,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31547,7 +31547,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31595,7 +31595,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tryckimpregnerat trä, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tryckimpregnerat trä, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31643,7 +31643,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Betong, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Betong, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31691,7 +31691,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Tegel, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31787,7 +31787,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31835,7 +31835,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Gips' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -31858,17 +31858,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -31878,12 +31878,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP TEST370VV score=0.29 justerad=0.39. Matchar waste_type: Plast. Skillnader category: Word='ÅVC/verksamhetsavfall' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', unit_type: Word='Vikt' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Gips, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -31906,17 +31906,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -31926,12 +31926,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest. Skillnader unit_type: Word='Volym' kandidat='Vikt', factor_hint: Word='VOLM' kandidat='VIKG'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -31979,7 +31979,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32075,7 +32075,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32098,17 +32098,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>SemanticDecisionEngine</t>
+          <t>Taxepunkter</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Ingen kandidat över granskningsgräns</t>
+          <t>Bästa semantiska kandidat saknar taxekod</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -32118,12 +32118,12 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>NEW_TAXA</t>
+          <t>REVIEW_REQUIRED</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP Miljövagn score=0.27 justerad=0.36. Matchar waste_type: Metall. Skillnader category: Word='ÅVC/verksamhetsavfall' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat='ÅRKV'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -32219,7 +32219,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -32242,17 +32242,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -32262,12 +32262,12 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Oljeavfall', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -32315,7 +32315,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.34 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32411,7 +32411,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.34 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32459,7 +32459,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang. Skillnader waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', property_type: Word='' kandidat='Verksamhet'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.41 justerad=0.41. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32507,7 +32507,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Volym' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32555,7 +32555,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, service_type: Abonnemang. Skillnader unit_type: Word='' kandidat='Vikt', factor_hint: Word='' kandidat='VIKG'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.51 justerad=0.56. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Vikt', factor_hint: Word='' kandidat='VIKG'</t>
         </is>
       </c>
     </row>
@@ -32578,17 +32578,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -32598,12 +32598,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Farligt avfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32651,7 +32651,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32699,7 +32699,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32747,7 +32747,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.52 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', container_volume_liter: Word='' kandidat='10', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32770,17 +32770,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -32790,12 +32790,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32818,17 +32818,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -32838,12 +32838,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32866,17 +32866,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -32886,12 +32886,12 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Slam' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -32987,7 +32987,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -33035,7 +33035,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.45 justerad=0.49. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.48 justerad=0.53. Matchar category: ÅVC/verksamhetsavfall, waste_type: Förpackningar, service_type: Abonnemang. Skillnader container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='', factor_hint: Word='VIKG' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -33154,17 +33154,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -33174,12 +33174,12 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33202,17 +33202,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -33222,12 +33222,12 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33250,17 +33250,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -33270,12 +33270,12 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33298,17 +33298,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -33318,12 +33318,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33346,17 +33346,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33394,17 +33394,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -33414,12 +33414,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33442,17 +33442,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -33462,12 +33462,12 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33490,17 +33490,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -33510,12 +33510,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33538,17 +33538,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -33558,12 +33558,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33586,17 +33586,17 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -33606,12 +33606,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33634,17 +33634,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -33654,12 +33654,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33682,17 +33682,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -33702,12 +33702,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33730,17 +33730,17 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -33750,12 +33750,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33778,17 +33778,17 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33826,17 +33826,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -33846,12 +33846,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33874,17 +33874,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -33894,12 +33894,12 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33922,17 +33922,17 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -33942,12 +33942,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -33995,7 +33995,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34043,7 +34043,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34091,7 +34091,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34187,7 +34187,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34283,7 +34283,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34331,7 +34331,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34379,7 +34379,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34427,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34475,7 +34475,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34523,7 +34523,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34571,7 +34571,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34619,7 +34619,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34667,7 +34667,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34715,7 +34715,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34763,7 +34763,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34811,7 +34811,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34859,7 +34859,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34907,7 +34907,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -34930,17 +34930,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -34950,12 +34950,12 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.56 justerad=0.61. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -34978,17 +34978,17 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -34998,12 +34998,12 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.56 justerad=0.61. Matchar category: ÅVC/verksamhetsavfall, waste_type: Oljeavfall, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Abonnemang', container_volume_liter: Word='' kandidat='10'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.44 justerad=0.44. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck, unit_type: Behållarvolym. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', factor_hint: Word='VOLYM/BEHÅLLARE' kandidat='ÅRKV'</t>
         </is>
       </c>
     </row>
@@ -35051,7 +35051,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35099,7 +35099,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35147,7 +35147,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35195,7 +35195,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35243,7 +35243,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35291,7 +35291,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35339,7 +35339,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35387,7 +35387,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35435,7 +35435,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35483,7 +35483,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35531,7 +35531,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35579,7 +35579,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35627,7 +35627,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.28 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='Batterier' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35675,7 +35675,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.28 justerad=0.34. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='Batterier' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35723,7 +35723,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -35771,7 +35771,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35867,7 +35867,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35915,7 +35915,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -35963,7 +35963,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.53 justerad=0.57. Matchar category: ÅVC/verksamhetsavfall, waste_type: Elavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36011,7 +36011,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36059,7 +36059,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.42 justerad=0.47. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36082,17 +36082,17 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -36102,12 +36102,12 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.38 justerad=0.43. Matchar category: ÅVC/verksamhetsavfall, waste_type: Kyl/frys. Skillnader unit_type: Word='Styck' kandidat='Vikt', factor_hint: Word='ST' kandidat='VIKG'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -36155,7 +36155,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Kyl/frys, unit_type: Vikt, factor_hint: VIKG. Skillnader property_type: Word='Verksamhet' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36203,7 +36203,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=STANDARD KÄ140RE26V score=0.30 justerad=0.30. Matchar category: ÅVC/verksamhetsavfall. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Abonnemang', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140'</t>
+          <t>Bästa kandidat var för svag. Kandidat=STANDARD SÄ160OS156 score=0.38 justerad=0.38. Matchar category: ÅVC/verksamhetsavfall, service_type: Abonnemang, container_type: Säck. Skillnader waste_type: Word='Asbest' kandidat='', container_volume_liter: Word='' kandidat='160', property_type: Word='Verksamhet' kandidat='', unit_type: Word='Styck' kandidat='Behållarvolym'</t>
         </is>
       </c>
     </row>
@@ -36251,7 +36251,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.40. Matchar category: ÅVC/verksamhetsavfall, unit_type: Vikt, factor_hint: VIKG. Skillnader waste_type: Word='' kandidat='Elavfall', service_type: Word='' kandidat='Abonnemang', property_type: Word='Verksamhet' kandidat=''</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.50 justerad=0.55. Matchar category: ÅVC/verksamhetsavfall, waste_type: Asbest, unit_type: Vikt, factor_hint: VIKG. Skillnader service_type: Word='Abonnemang' kandidat='', container_type: Word='Säck' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36299,7 +36299,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader container_volume_liter: Word='' kandidat='3m3'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.40 justerad=0.45. Matchar category: Verksamhetsavfall, container_type: Container, unit_type: Volym, factor_hint: VOLM. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36443,7 +36443,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Verksamhetsavfall, container_type: Container. Skillnader container_volume_liter: Word='' kandidat='3m3', unit_type: Word='' kandidat='Volym', factor_hint: Word='' kandidat='VOLM'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.31 justerad=0.36. Matchar category: Verksamhetsavfall, container_type: Container. Skillnader waste_type: Word='Asbest' kandidat='', service_type: Word='Abonnemang' kandidat='', container_volume_liter: Word='' kandidat='3m3', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36491,7 +36491,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP EJKLASSFA score=0.37 justerad=0.47. Matchar waste_type: Farligt avfall, service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', unit_type: Word='' kandidat='Tillfälle', factor_hint: Word='' kandidat='KVAN'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP EJKLASSFA score=0.37 justerad=0.47. Matchar waste_type: Farligt avfall, service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat='', unit_type: Word='' kandidat='Tillfälle'</t>
         </is>
       </c>
     </row>
@@ -36539,7 +36539,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar waste_type: Farligt avfall, service_type: Abonnemang, unit_type: Tillfälle, factor_hint: TILLFÄLLE. Skillnader category: Word='Verksamhetsavfall' kandidat='Hushåll'</t>
+          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.46 justerad=0.51. Matchar waste_type: Farligt avfall, service_type: Abonnemang, unit_type: Tillfälle, factor_hint: TILLFÄLLE. Skillnader category: Word='Verksamhetsavfall' kandidat='Hushåll', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36562,17 +36562,17 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Taxepunkter</t>
+          <t>SemanticDecisionEngine</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Bästa semantiska kandidat saknar taxekod</t>
+          <t>Ingen kandidat över granskningsgräns</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -36582,12 +36582,12 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>REVIEW_REQUIRED</t>
+          <t>NEW_TAXA</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.26 justerad=0.31. Matchar category: Verksamhetsavfall, unit_type: Tillfälle, factor_hint: TILLFÄLLE</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RK26FRI score=0.24 justerad=0.34. Matchar service_type: Abonnemang. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', waste_type: Word='' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
+          <t>Bästa kandidat var för svag. Kandidat=RULE:EDP BYGGRIVTRÄ score=0.24 justerad=0.34. Matchar waste_type: Träavfall. Skillnader category: Word='Verksamhetsavfall' kandidat='Okänd', service_type: Word='Abonnemang' kandidat='', container_type: Word='Container' kandidat='', property_type: Word='Verksamhet' kandidat=''</t>
         </is>
       </c>
     </row>

--- a/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
+++ b/output/excel/ArbetsExcel_byggd_fran_parser.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Avviker_Standard" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_Knowledge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision_Trace" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbook_Generation" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxepunkter'!$A$1:$J$242</definedName>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +70,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -92,6 +103,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -266,6 +280,23 @@
     <tableColumn id="13" name="Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DecisionTraceTable" displayName="DecisionTraceTable" ref="A5:H64" headerRowCount="1">
+  <autoFilter ref="A5:H64"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Word taxekod"/>
+    <tableColumn id="2" name="Kandidat taxekod"/>
+    <tableColumn id="3" name="Beslut"/>
+    <tableColumn id="4" name="Säkerhet"/>
+    <tableColumn id="5" name="Totalpoäng"/>
+    <tableColumn id="6" name="Primär motivering"/>
+    <tableColumn id="7" name="Avvisningsorsak"/>
+    <tableColumn id="8" name="Signaler"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
 </table>
 </file>
 
@@ -558,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M242"/>
+  <dimension ref="A1:Q242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -574,6 +605,10 @@
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -642,6 +677,26 @@
           <t>Beslutskommentar</t>
         </is>
       </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Beslutsspår kandidat</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>Beslutsspår status</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Beslutsspår säkerhet</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Beslutsspår motivering</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -684,6 +739,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -726,6 +799,24 @@
           <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O3" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -768,6 +859,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -815,6 +924,24 @@
           <t>Manuell granskning krävs på grund av liten skillnad mellan kandidater. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.86 justerad=0.91. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -862,6 +989,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -904,6 +1049,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Extra. Skillnader waste_type: Word='Träavfall' kandidat='Restavfall', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='190', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -946,6 +1109,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -993,6 +1174,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Byte. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1040,6 +1239,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370FP score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1082,6 +1299,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1129,6 +1364,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1171,6 +1424,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1213,6 +1484,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1255,6 +1544,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190FP52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1297,6 +1604,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370FP52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1339,6 +1664,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660FP52FV score=0.76 justerad=0.81. Matchar category: Hushåll, waste_type: Förpackningar, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='Abonnemang' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1381,6 +1724,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.58 justerad=0.63. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='Abonnemang' kandidat='Extra'</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1428,6 +1789,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370FP score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Abonnemang, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1475,6 +1854,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT GEMUPPMRFPFLB score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1522,6 +1919,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1569,6 +1984,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SLT03SLBUD</t>
+        </is>
+      </c>
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1616,6 +2049,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SLT03SLORD</t>
+        </is>
+      </c>
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1663,6 +2114,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SLT36SLBUD</t>
+        </is>
+      </c>
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1710,6 +2179,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT GEMUPPMRFPFLB score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SLT36SLORD</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1757,6 +2244,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT GEMUPPMRFPFLB score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SLT03SL</t>
+        </is>
+      </c>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1804,6 +2309,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SLT36SL</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1846,6 +2369,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NYMAT</t>
+        </is>
+      </c>
+      <c r="O28" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1893,6 +2434,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GROVBUD</t>
+        </is>
+      </c>
+      <c r="O29" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1940,6 +2499,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1987,6 +2564,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT GEMUPPMRFPFLB score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2034,6 +2629,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT GEMUPPMRFPFLB score=0.49 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall, service_type: Abonnemang. Skillnader property_type: Word='' kandidat='Flerbostadshus'</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2076,6 +2689,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Matavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ÅBEHGF</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2118,6 +2749,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ÅBEHGO</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2165,6 +2814,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ÅBEHME</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2212,6 +2879,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Matavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='140', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>ÅBEHPA</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2259,6 +2944,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.50 justerad=0.55. Matchar category: Hushåll, waste_type: Restavfall. Skillnader service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ÅBEHPL</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2306,6 +3009,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ÅTÖMGF</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2348,6 +3069,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ÅTÖMGO</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2390,6 +3129,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:EDP KÄ240RM26FRI score=0.54 justerad=0.64. Matchar waste_type: Matavfall, container_type: Kärl, container_volume_liter: 240. Skillnader category: Word='Hushåll' kandidat='Okänd', service_type: Word='' kandidat='Abonnemang', property_type: Word='' kandidat='Fritidshus', unit_type: Word='Vikt' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ÅTÖMME</t>
+        </is>
+      </c>
+      <c r="O40" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2437,6 +3194,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 240. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ÅTÖMPA</t>
+        </is>
+      </c>
+      <c r="O41" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2479,6 +3254,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Matavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 140. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ÅTÖMPL</t>
+        </is>
+      </c>
+      <c r="O42" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2521,6 +3314,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.74 justerad=0.79. Matchar category: Hushåll, waste_type: Restavfall, service_type: Extra, container_type: Kärl, container_volume_liter: 190. Skillnader unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ÅVSGF</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2563,6 +3374,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 370. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>ÅVSGO</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2605,6 +3434,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.67 justerad=0.71. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 660. Skillnader service_type: Word='' kandidat='Hämtning/tömning', unit_type: Word='Vikt' kandidat='Behållarvolym', factor_hint: Word='VIKG' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ÅVSME</t>
+        </is>
+      </c>
+      <c r="O45" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2652,6 +3499,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ÅVSPA</t>
+        </is>
+      </c>
+      <c r="O46" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2694,6 +3559,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370FP score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ÅVSPL</t>
+        </is>
+      </c>
+      <c r="O47" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2741,6 +3624,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader waste_type: Word='Träavfall' kandidat='', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>BDT03SLBUD</t>
+        </is>
+      </c>
+      <c r="O48" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2788,6 +3689,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 240, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>BDT03SLORD</t>
+        </is>
+      </c>
+      <c r="O49" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2835,6 +3754,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.62 justerad=0.67. Matchar category: Hushåll, service_type: Byte, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>BRN03SLBUD</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2882,6 +3819,24 @@
           <t>Kandidaten kan ge beslutsstöd men saknar taxekod. Kandidat=RULE:TAXEPUNKT  score=0.41 justerad=0.46. Matchar category: Hushåll, service_type: Byte, container_type: Kärl. Skillnader container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>BRN03SLORD</t>
+        </is>
+      </c>
+      <c r="O51" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2929,6 +3884,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.40 justerad=0.45. Matchar category: Hushåll, container_type: Kärl. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_volume_liter: Word='' kandidat='240', unit_type: Word='' kandidat='Behållarvolym'</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>BRN36SLBUD</t>
+        </is>
+      </c>
+      <c r="O52" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2976,6 +3949,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ370FP score=0.34 justerad=0.39. Matchar category: Hushåll, service_type: Abonnemang. Skillnader container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='370', unit_type: Word='' kandidat='Behållarvolym', factor_hint: Word='' kandidat='VOLYM/BEHÅLLARE'</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>BRN36SLORD</t>
+        </is>
+      </c>
+      <c r="O53" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3023,6 +4014,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>BDT03SL</t>
+        </is>
+      </c>
+      <c r="O54" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3065,6 +4074,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>BRN03SL</t>
+        </is>
+      </c>
+      <c r="O55" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3112,6 +4139,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ660RE52FV score=0.60 justerad=0.66. Matchar category: Hushåll, container_type: Kärl, container_volume_liter: 660, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>BRN36SL</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3159,6 +4204,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>MRV03SLBUD</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3206,6 +4269,24 @@
           <t>Bästa kandidat var för svag. Kandidat=RULE:TAXEPUNKT KÄ240RM26 score=0.32 justerad=0.37. Matchar category: Hushåll. Skillnader waste_type: Word='' kandidat='Restavfall', service_type: Word='' kandidat='Hämtning/tömning', container_type: Word='' kandidat='Kärl', container_volume_liter: Word='' kandidat='240'</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>MRV03SLORD</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3253,6 +4334,24 @@
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ140MA52FV score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Matavfall, container_type: Kärl, container_volume_liter: 140, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Hämtning/tömning'</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>MRV36SLBUD</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3298,6 +4397,24 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>Granska kandidat manuellt. Kandidat=RULE:TAXEPUNKT KÄ190XRM26 score=0.79 justerad=0.83. Matchar category: Hushåll, waste_type: Restavfall, container_type: Kärl, container_volume_liter: 190, unit_type: Behållarvolym, factor_hint: VOLYM/BEHÅLLARE. Skillnader service_type: Word='' kandidat='Extra'</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>MRV36SLORD</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
         </is>
       </c>
     </row>
@@ -24328,7 +25445,6 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
       <c r="B254" t="inlineStr">
         <is>
           <t>2.2.1</t>
@@ -24376,7 +25492,6 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
       <c r="B255" t="inlineStr">
         <is>
           <t>2.2.1</t>
@@ -24424,7 +25539,6 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
       <c r="B256" t="inlineStr">
         <is>
           <t>2.2.2</t>
@@ -24472,7 +25586,6 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr">
         <is>
           <t>2.2.2</t>
@@ -24520,7 +25633,6 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
           <t>2.2.3</t>
@@ -24568,7 +25680,6 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
           <t>2.2.3</t>
@@ -24616,7 +25727,6 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
           <t>2.2.3</t>
@@ -24664,7 +25774,6 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
           <t>2.2.3</t>
@@ -24712,7 +25821,6 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
           <t>2.2.3</t>
@@ -24760,7 +25868,6 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -24808,7 +25915,6 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -24856,7 +25962,6 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -24904,7 +26009,6 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -24952,7 +26056,6 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25000,7 +26103,6 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25048,7 +26150,6 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25096,7 +26197,6 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25144,7 +26244,6 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25192,7 +26291,6 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
           <t>2.2.4</t>
@@ -25240,7 +26338,6 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25288,7 +26385,6 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25336,7 +26432,6 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25384,7 +26479,6 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25432,7 +26526,6 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25480,7 +26573,6 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
           <t>2.2.5</t>
@@ -25528,7 +26620,6 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25576,7 +26667,6 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25624,7 +26714,6 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25672,7 +26761,6 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25720,7 +26808,6 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25768,7 +26855,6 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
           <t>2.2.6</t>
@@ -25816,7 +26902,6 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
           <t>2.2.7</t>
@@ -25864,7 +26949,6 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
           <t>2.2.7</t>
@@ -25912,7 +26996,6 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
           <t>2.2.7</t>
@@ -25960,7 +27043,6 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -26008,7 +27090,6 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -26056,7 +27137,6 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -26104,7 +27184,6 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
           <t>2.4.1</t>
@@ -26152,7 +27231,6 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26200,7 +27278,6 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26248,7 +27325,6 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26296,7 +27372,6 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26344,7 +27419,6 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26392,7 +27466,6 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
           <t>2.4.2</t>
@@ -26440,7 +27513,6 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
           <t>2.4.3</t>
@@ -26488,7 +27560,6 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
           <t>2.4.3</t>
@@ -26536,7 +27607,6 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
           <t>2.4.4</t>
@@ -26584,7 +27654,6 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
           <t>2.4.5</t>
@@ -26632,7 +27701,6 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
           <t>2.4.5</t>
@@ -26680,7 +27748,6 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
           <t>2.4.5</t>
@@ -26728,7 +27795,6 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
           <t>2.4.6</t>
@@ -26776,7 +27842,6 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr">
         <is>
           <t>2.4.6</t>
@@ -26824,7 +27889,6 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
       <c r="B306" t="inlineStr">
         <is>
           <t>2.4.7</t>
@@ -26872,7 +27936,6 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr">
         <is>
           <t>2.4.7</t>
@@ -26920,7 +27983,6 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr"/>
       <c r="B308" t="inlineStr">
         <is>
           <t>2.4.7</t>
@@ -26968,7 +28030,6 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
       <c r="B309" t="inlineStr">
         <is>
           <t>2.4.7</t>
@@ -27016,7 +28077,6 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr">
         <is>
           <t>2.4.7</t>
@@ -27064,7 +28124,6 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr"/>
       <c r="B311" t="inlineStr">
         <is>
           <t>2.4.8</t>
@@ -27112,7 +28171,6 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr"/>
       <c r="B312" t="inlineStr">
         <is>
           <t>2.4.8</t>
@@ -27160,7 +28218,6 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr"/>
       <c r="B313" t="inlineStr">
         <is>
           <t>2.4.8</t>
@@ -27208,7 +28265,6 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr"/>
       <c r="B314" t="inlineStr">
         <is>
           <t>2.4.8</t>
@@ -27256,7 +28312,6 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr">
         <is>
           <t>2.4.8</t>
@@ -27304,7 +28359,6 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr"/>
       <c r="B316" t="inlineStr">
         <is>
           <t>2.4.9</t>
@@ -27352,7 +28406,6 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr">
         <is>
           <t>2.4.9</t>
@@ -27400,7 +28453,6 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr">
         <is>
           <t>2.4.9</t>
@@ -27448,7 +28500,6 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr"/>
       <c r="B319" t="inlineStr">
         <is>
           <t>2.4.10</t>
@@ -27496,7 +28547,6 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
       <c r="B320" t="inlineStr">
         <is>
           <t>2.4.10</t>
@@ -27544,7 +28594,6 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr">
         <is>
           <t>2.4.11</t>
@@ -27592,7 +28641,6 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr"/>
       <c r="B322" t="inlineStr">
         <is>
           <t>2.4.11</t>
@@ -27640,7 +28688,6 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr"/>
       <c r="B323" t="inlineStr">
         <is>
           <t>2.4.11</t>
@@ -27688,7 +28735,6 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr">
         <is>
           <t>2.4.11</t>
@@ -27736,7 +28782,6 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr"/>
       <c r="B325" t="inlineStr">
         <is>
           <t>2.5.1</t>
@@ -27784,7 +28829,6 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr">
         <is>
           <t>2.5.1</t>
@@ -27832,7 +28876,6 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr"/>
       <c r="B327" t="inlineStr">
         <is>
           <t>2.5.1</t>
@@ -27880,7 +28923,6 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr"/>
       <c r="B328" t="inlineStr">
         <is>
           <t>2.5.1</t>
@@ -27928,7 +28970,6 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr"/>
       <c r="B329" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -27976,7 +29017,6 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
       <c r="B330" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -28024,7 +29064,6 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr"/>
       <c r="B331" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -28072,7 +29111,6 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr"/>
       <c r="B332" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -28120,7 +29158,6 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr"/>
       <c r="B333" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -28168,7 +29205,6 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr"/>
       <c r="B334" t="inlineStr">
         <is>
           <t>3.1</t>
@@ -28216,7 +29252,6 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
       <c r="B335" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28264,7 +29299,6 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
       <c r="B336" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28312,7 +29346,6 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr"/>
       <c r="B337" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28360,7 +29393,6 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr"/>
       <c r="B338" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28408,7 +29440,6 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr"/>
       <c r="B339" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28456,7 +29487,6 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr"/>
       <c r="B340" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28504,7 +29534,6 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28552,7 +29581,6 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr"/>
       <c r="B342" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28600,7 +29628,6 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr"/>
       <c r="B343" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28648,7 +29675,6 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -28696,7 +29722,6 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -28744,7 +29769,6 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -28792,7 +29816,6 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -28840,7 +29863,6 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -28888,7 +29910,6 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -28936,7 +29957,6 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr"/>
       <c r="B350" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -28984,7 +30004,6 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr"/>
       <c r="B351" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -29032,7 +30051,6 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr"/>
       <c r="B352" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -29080,7 +30098,6 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr"/>
       <c r="B353" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -29128,7 +30145,6 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr"/>
       <c r="B354" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -29176,7 +30192,6 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr"/>
       <c r="B355" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -29224,7 +30239,6 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr"/>
       <c r="B356" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -29272,7 +30286,6 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr"/>
       <c r="B357" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29320,7 +30333,6 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr"/>
       <c r="B358" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29368,7 +30380,6 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29416,7 +30427,6 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr"/>
       <c r="B360" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29464,7 +30474,6 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr"/>
       <c r="B361" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29512,7 +30521,6 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr"/>
       <c r="B362" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29560,7 +30568,6 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr"/>
       <c r="B363" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29608,7 +30615,6 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29656,7 +30662,6 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr"/>
       <c r="B365" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29704,7 +30709,6 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr"/>
       <c r="B366" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29752,7 +30756,6 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr"/>
       <c r="B367" t="inlineStr">
         <is>
           <t>5.2</t>
@@ -29800,7 +30803,6 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr"/>
       <c r="B368" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -29848,7 +30850,6 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr"/>
       <c r="B369" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -29896,7 +30897,6 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr"/>
       <c r="B370" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -29944,7 +30944,6 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr"/>
       <c r="B371" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -29992,7 +30991,6 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -30040,7 +31038,6 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -30088,7 +31085,6 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr"/>
       <c r="B374" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -30136,7 +31132,6 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr"/>
       <c r="B375" t="inlineStr">
         <is>
           <t>6.1.1</t>
@@ -30184,7 +31179,6 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr"/>
       <c r="B376" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30232,7 +31226,6 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr"/>
       <c r="B377" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30280,7 +31273,6 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr"/>
       <c r="B378" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30328,7 +31320,6 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30376,7 +31367,6 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr"/>
       <c r="B380" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30424,7 +31414,6 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr"/>
       <c r="B381" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30472,7 +31461,6 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr"/>
       <c r="B382" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30520,7 +31508,6 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr"/>
       <c r="B383" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30568,7 +31555,6 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
       <c r="B384" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30616,7 +31602,6 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30664,7 +31649,6 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr"/>
       <c r="B386" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30712,7 +31696,6 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30760,7 +31743,6 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr"/>
       <c r="B388" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30808,7 +31790,6 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30856,7 +31837,6 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr"/>
       <c r="B390" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30904,7 +31884,6 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -30952,7 +31931,6 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr"/>
       <c r="B392" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31000,7 +31978,6 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31048,7 +32025,6 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr"/>
       <c r="B394" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31096,7 +32072,6 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr"/>
       <c r="B395" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31144,7 +32119,6 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31192,7 +32166,6 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr"/>
       <c r="B397" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31240,7 +32213,6 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr"/>
       <c r="B398" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31288,7 +32260,6 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr"/>
       <c r="B399" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31336,7 +32307,6 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr"/>
       <c r="B400" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31384,7 +32354,6 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr"/>
       <c r="B401" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31432,7 +32401,6 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr"/>
       <c r="B402" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31480,7 +32448,6 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr"/>
       <c r="B403" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31528,7 +32495,6 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr"/>
       <c r="B404" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31576,7 +32542,6 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr"/>
       <c r="B405" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31624,7 +32589,6 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr"/>
       <c r="B406" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31672,7 +32636,6 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr"/>
       <c r="B407" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31720,7 +32683,6 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31768,7 +32730,6 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr"/>
       <c r="B409" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31816,7 +32777,6 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr"/>
       <c r="B410" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31864,7 +32824,6 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr"/>
       <c r="B411" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31912,7 +32871,6 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr"/>
       <c r="B412" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -31960,7 +32918,6 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32008,7 +32965,6 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr"/>
       <c r="B414" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32056,7 +33012,6 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr"/>
       <c r="B415" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32104,7 +33059,6 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr"/>
       <c r="B416" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32152,7 +33106,6 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr"/>
       <c r="B417" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32200,7 +33153,6 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr"/>
       <c r="B418" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32248,7 +33200,6 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr"/>
       <c r="B419" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32296,7 +33247,6 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr"/>
       <c r="B420" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32344,7 +33294,6 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr"/>
       <c r="B421" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32392,7 +33341,6 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32440,7 +33388,6 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr"/>
       <c r="B423" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32488,7 +33435,6 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr"/>
       <c r="B424" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32536,7 +33482,6 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr"/>
       <c r="B425" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32584,7 +33529,6 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr"/>
       <c r="B426" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32632,7 +33576,6 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr"/>
       <c r="B427" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32680,7 +33623,6 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr"/>
       <c r="B428" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32728,7 +33670,6 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32776,7 +33717,6 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr"/>
       <c r="B430" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32824,7 +33764,6 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32872,7 +33811,6 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr"/>
       <c r="B432" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32920,7 +33858,6 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -32968,7 +33905,6 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr"/>
       <c r="B434" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33016,7 +33952,6 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr"/>
       <c r="B435" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33064,7 +33999,6 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr"/>
       <c r="B436" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33112,7 +34046,6 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33160,7 +34093,6 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr"/>
       <c r="B438" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33208,7 +34140,6 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr"/>
       <c r="B439" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33256,7 +34187,6 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr"/>
       <c r="B440" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33304,7 +34234,6 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr"/>
       <c r="B441" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33352,7 +34281,6 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr"/>
       <c r="B442" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33400,7 +34328,6 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr"/>
       <c r="B443" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33448,7 +34375,6 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33496,7 +34422,6 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33544,7 +34469,6 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33592,7 +34516,6 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr"/>
       <c r="B447" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33640,7 +34563,6 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr"/>
       <c r="B448" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33688,7 +34610,6 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33736,7 +34657,6 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr"/>
       <c r="B450" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33784,7 +34704,6 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr"/>
       <c r="B451" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33832,7 +34751,6 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr"/>
       <c r="B452" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33880,7 +34798,6 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr"/>
       <c r="B453" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33928,7 +34845,6 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr"/>
       <c r="B454" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -33976,7 +34892,6 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
       <c r="B455" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34024,7 +34939,6 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr"/>
       <c r="B456" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34072,7 +34986,6 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr"/>
       <c r="B457" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34120,7 +35033,6 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr"/>
       <c r="B458" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34168,7 +35080,6 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr"/>
       <c r="B459" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34216,7 +35127,6 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr"/>
       <c r="B460" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34264,7 +35174,6 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr"/>
       <c r="B461" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34312,7 +35221,6 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr"/>
       <c r="B462" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34360,7 +35268,6 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr"/>
       <c r="B463" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34408,7 +35315,6 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr"/>
       <c r="B464" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34456,7 +35362,6 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr"/>
       <c r="B465" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34504,7 +35409,6 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr"/>
       <c r="B466" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34552,7 +35456,6 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr"/>
       <c r="B467" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34600,7 +35503,6 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34648,7 +35550,6 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34696,7 +35597,6 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34744,7 +35644,6 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr"/>
       <c r="B471" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34792,7 +35691,6 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr"/>
       <c r="B472" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34840,7 +35738,6 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr"/>
       <c r="B473" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34888,7 +35785,6 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr"/>
       <c r="B474" t="inlineStr">
         <is>
           <t>6.1.2</t>
@@ -34936,7 +35832,6 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr">
         <is>
           <t>6.1.3</t>
@@ -34984,7 +35879,6 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr"/>
       <c r="B476" t="inlineStr">
         <is>
           <t>6.1.3</t>
@@ -35032,7 +35926,6 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr">
         <is>
           <t>6.1.3</t>
@@ -35080,7 +35973,6 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr">
         <is>
           <t>6.1.3</t>
@@ -35128,7 +36020,6 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr">
         <is>
           <t>6.1.4</t>
@@ -35176,7 +36067,6 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr">
         <is>
           <t>6.1.4</t>
@@ -35224,7 +36114,6 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr"/>
       <c r="B481" t="inlineStr">
         <is>
           <t>6.1.4</t>
@@ -35272,7 +36161,6 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr"/>
       <c r="B482" t="inlineStr">
         <is>
           <t>6.1.4</t>
@@ -47462,4 +48350,2211 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Decision_Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Spårbar beslutskedja från Word/parser till kandidat och beslutsmotivering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Regel</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Taxa_från_edp är facit och ändras aldrig automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Word taxekod</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Kandidat taxekod</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Beslut</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Säkerhet</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Totalpoäng</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Primär motivering</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Avvisningsorsak</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Signaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:1.00*0.05=0.0500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:1.00*0.05=0.0500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>SLSLANG</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.2000: Samma taxefamilj och inga identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:1.00*0.20=0.2000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>KÄ660RE52FV</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; variant bidrar 0.1820: Samma taxefamilj men identifierade variantavvikelser.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.91*0.20=0.1820 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SLBUD</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SLBUD</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SLORD</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SLORD</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SLBUD</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SLBUD</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SLORD</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SLORD</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SL</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>SLT03SL</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SL</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>SLT36SL</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ACCEPT</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; tax_family bidrar 0.1500: Samma taxefamilj och samma variant/intervall.; variant bidrar 0.1100: Samma taxefamilj men identifierade variantavvikelser.</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:1.00*0.15=0.1500 | variant:0.55*0.20=0.1100 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>NYMAT</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>NYMAT</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>GROVBUD</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>GROVBUD</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>MB1600MA26</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHGF</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHGF</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHGO</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHGO</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHME</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHME</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHPA</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHPA</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHPL</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>ÅBEHPL</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMGF</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMGF</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMGO</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMGO</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMME</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMME</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMPA</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMPA</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMPL</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>ÅTÖMPL</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSGF</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSGF</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSGO</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSGO</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSME</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSME</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSPA</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSPA</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSPL</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>ÅVSPL</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; variant bidrar 0.0900: Olika taxefamiljer. Variantjämförelse ska inte användas som match.</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.45*0.20=0.0900 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SLBUD</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SLBUD</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SLORD</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SLORD</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SLBUD</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SLBUD</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SLORD</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SLORD</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SLBUD</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SLBUD</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SLORD</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SLORD</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SL</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>BDT03SL</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SL</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>BRN03SL</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SL</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>BRN36SL</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>MRV03SLBUD</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>MRV03SLBUD</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>MRV03SLORD</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>MRV03SLORD</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>MRV36SLBUD</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>MRV36SLBUD</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>MRV36SLORD</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>MRV36SLORD</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact bidrar 0.3000: Direkt träff mot Taxa_från_edp.; hierarchical_context bidrar 0.1000: Samma hierarkiska kontext.; tax_family bidrar 0.0000: Olika taxefamiljer.</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>edp_exact:1.00*0.30=0.3000 | tax_family:0.00*0.15=0.0000 | variant:0.00*0.20=0.0000 | semantic_attributes:0.00*0.20=0.0000 | hierarchical_context:1.00*0.10=0.1000 | document_structure:0.00*0.05=0.0000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Workbook Generation Engine Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>output\excel\ArbetsExcel_byggd_fran_parser.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Decision trace input rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Decision_Trace rows written</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Taxepunkter rows updated</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warnings</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Regel</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Taxa_från_edp ändras inte. Beslutsspår är beslutsstöd för granskning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>